--- a/Proyecto_Python/src/main/resources/matrices/matrix_Caso2_32x32.xlsx
+++ b/Proyecto_Python/src/main/resources/matrices/matrix_Caso2_32x32.xlsx
@@ -660,100 +660,100 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9964517</v>
+        <v>4881073</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1670831</v>
+        <v>2378575</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1750017</v>
+        <v>5672972</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2823690</v>
+        <v>8169779</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1089409</v>
+        <v>8151562</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9590367</v>
+        <v>4897090</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>602664</v>
+        <v>7419920</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>8303918</v>
+        <v>8089623</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1478775</v>
+        <v>4503299</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>7156454</v>
+        <v>2322410</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>8345347</v>
+        <v>5178655</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>9880310</v>
+        <v>23570</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>2726821</v>
+        <v>7533819</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2010558</v>
+        <v>6424108</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>6195906</v>
+        <v>3281737</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>5621516</v>
+        <v>7422693</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>8033778</v>
+        <v>8303674</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4654863</v>
+        <v>8624695</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>6461847</v>
+        <v>3255331</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>9817769</v>
+        <v>1904912</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>6449454</v>
+        <v>8607166</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>2482753</v>
+        <v>4742521</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>8623620</v>
+        <v>8044940</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>5932224</v>
+        <v>6727669</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>5754237</v>
+        <v>9700246</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>5694478</v>
+        <v>2065600</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>698994</v>
+        <v>5242561</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>1680435</v>
+        <v>3383889</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>5103004</v>
+        <v>8739444</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>328741</v>
+        <v>5114480</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>7751881</v>
+        <v>308659</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>106248</v>
+        <v>4590757</v>
       </c>
     </row>
     <row r="5">
@@ -763,100 +763,100 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7938167</v>
+        <v>238779</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7921573</v>
+        <v>7002324</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7221689</v>
+        <v>2075656</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>8409715</v>
+        <v>7047933</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5099040</v>
+        <v>8762051</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8401355</v>
+        <v>2253779</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1953849</v>
+        <v>8017516</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>9065821</v>
+        <v>9116638</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2596947</v>
+        <v>3226851</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8638356</v>
+        <v>4137449</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>3962662</v>
+        <v>215473</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1131606</v>
+        <v>1615964</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>8085678</v>
+        <v>933866</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>6268123</v>
+        <v>5518996</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>5314823</v>
+        <v>726906</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>440197</v>
+        <v>7206863</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>4755825</v>
+        <v>7897630</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>8217883</v>
+        <v>4855141</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>9300052</v>
+        <v>7096648</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>671915</v>
+        <v>7209771</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>4782236</v>
+        <v>3647402</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>4603787</v>
+        <v>9962644</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>512324</v>
+        <v>9982139</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7956279</v>
+        <v>2205806</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>109123</v>
+        <v>8113278</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>3364115</v>
+        <v>4695027</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>2057961</v>
+        <v>2434656</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>7067355</v>
+        <v>692772</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1755352</v>
+        <v>5495540</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>4795913</v>
+        <v>8152203</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>7299141</v>
+        <v>3314763</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>2557936</v>
+        <v>5742743</v>
       </c>
     </row>
     <row r="6">
@@ -866,100 +866,100 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3148618</v>
+        <v>1886074</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>146174</v>
+        <v>1391869</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2614238</v>
+        <v>7111563</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4283632</v>
+        <v>6779419</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3080910</v>
+        <v>9494502</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6603004</v>
+        <v>8907260</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7280893</v>
+        <v>1885660</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>993201</v>
+        <v>8623714</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2517459</v>
+        <v>1248694</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8525192</v>
+        <v>4681319</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>8919669</v>
+        <v>8874839</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1523467</v>
+        <v>3638491</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1936480</v>
+        <v>4782223</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>6696313</v>
+        <v>7499929</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2136811</v>
+        <v>2392105</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2327541</v>
+        <v>8763966</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>1418147</v>
+        <v>3857118</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>8995207</v>
+        <v>2799864</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>3173736</v>
+        <v>5879917</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>7964012</v>
+        <v>1615809</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>6500154</v>
+        <v>7155356</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>8188315</v>
+        <v>7889820</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>8716813</v>
+        <v>408036</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1157767</v>
+        <v>5058863</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1946394</v>
+        <v>4813063</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>5851489</v>
+        <v>4199691</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>4803443</v>
+        <v>7576543</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>9828122</v>
+        <v>5245936</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>5866847</v>
+        <v>4507712</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>1134381</v>
+        <v>2551215</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>7444230</v>
+        <v>4031047</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>1797401</v>
+        <v>6909366</v>
       </c>
     </row>
     <row r="7">
@@ -969,100 +969,100 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3343067</v>
+        <v>7003187</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1447907</v>
+        <v>3231504</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8274485</v>
+        <v>6683303</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>825859</v>
+        <v>670793</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6859483</v>
+        <v>757120</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7755450</v>
+        <v>1503631</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6560698</v>
+        <v>7542041</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>9400632</v>
+        <v>2226842</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8572878</v>
+        <v>9919342</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4125177</v>
+        <v>3449221</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1613442</v>
+        <v>6495597</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>3569735</v>
+        <v>6315062</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>6283468</v>
+        <v>860129</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>3059285</v>
+        <v>4343395</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>3167566</v>
+        <v>1785590</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>8147104</v>
+        <v>7285443</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>9575457</v>
+        <v>4086568</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>8907902</v>
+        <v>2924677</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>7734286</v>
+        <v>988747</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>1345824</v>
+        <v>7643053</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>274270</v>
+        <v>4993651</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>26065</v>
+        <v>8721552</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>2621315</v>
+        <v>7293825</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>167976</v>
+        <v>9226307</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3119425</v>
+        <v>3179626</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>5622219</v>
+        <v>7045050</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>6757545</v>
+        <v>889643</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>8187455</v>
+        <v>6515609</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>7563521</v>
+        <v>9538013</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>4170299</v>
+        <v>1246287</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>7928086</v>
+        <v>4836776</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>1666589</v>
+        <v>1984837</v>
       </c>
     </row>
     <row r="8">
@@ -1072,100 +1072,100 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1732778</v>
+        <v>9089941</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8638694</v>
+        <v>8143295</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>7270087</v>
+        <v>5677861</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5877234</v>
+        <v>364203</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>470240</v>
+        <v>8803898</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>580806</v>
+        <v>4574265</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>3081908</v>
+        <v>9078136</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1893238</v>
+        <v>7533438</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>8657619</v>
+        <v>4720519</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>3354259</v>
+        <v>2851844</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>3303711</v>
+        <v>8476266</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>263743</v>
+        <v>5767272</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>6504578</v>
+        <v>5532227</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>8357518</v>
+        <v>1067539</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8957424</v>
+        <v>469185</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>6309911</v>
+        <v>1830709</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>767392</v>
+        <v>6206004</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>3444049</v>
+        <v>4367701</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>1202723</v>
+        <v>6531711</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>6289620</v>
+        <v>4841508</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>3056329</v>
+        <v>6066861</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>3242875</v>
+        <v>4786165</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>8726675</v>
+        <v>143940</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>9382531</v>
+        <v>195445</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>6745281</v>
+        <v>3942361</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>5662581</v>
+        <v>3385366</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>5387041</v>
+        <v>7856125</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>9088030</v>
+        <v>2779678</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>5394074</v>
+        <v>4633385</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>2821984</v>
+        <v>8631483</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>4578887</v>
+        <v>7136073</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>9301302</v>
+        <v>8570348</v>
       </c>
     </row>
     <row r="9">
@@ -1175,100 +1175,100 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5840547</v>
+        <v>5523983</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5072698</v>
+        <v>6766698</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2387885</v>
+        <v>3237333</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6523792</v>
+        <v>4568860</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9395979</v>
+        <v>7562717</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1484172</v>
+        <v>372383</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5267334</v>
+        <v>6404917</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9802296</v>
+        <v>9518099</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>810393</v>
+        <v>6098531</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7147944</v>
+        <v>4966818</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1195330</v>
+        <v>7957229</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>6722478</v>
+        <v>6373394</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8282891</v>
+        <v>3302130</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>9766548</v>
+        <v>8737936</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>5688160</v>
+        <v>7665613</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1032571</v>
+        <v>6690486</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>6220977</v>
+        <v>5900580</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>3632823</v>
+        <v>8994163</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3603776</v>
+        <v>5529319</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1899988</v>
+        <v>8230622</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>7256155</v>
+        <v>5408970</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>2420611</v>
+        <v>5992227</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8780879</v>
+        <v>2192</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>4729794</v>
+        <v>9466832</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>4228808</v>
+        <v>2237519</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>7772885</v>
+        <v>7693909</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>9678293</v>
+        <v>921456</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>4818569</v>
+        <v>15316</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>1063093</v>
+        <v>9929944</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>2768872</v>
+        <v>5031397</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>75465</v>
+        <v>362144</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>7370051</v>
+        <v>6205249</v>
       </c>
     </row>
     <row r="10">
@@ -1278,100 +1278,100 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4088128</v>
+        <v>6409889</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7657561</v>
+        <v>6312456</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9114865</v>
+        <v>961675</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>6058525</v>
+        <v>4763747</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1245937</v>
+        <v>5116051</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>7184634</v>
+        <v>9901133</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2378829</v>
+        <v>6087510</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>9115713</v>
+        <v>9407991</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>6230048</v>
+        <v>3276233</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3253934</v>
+        <v>321029</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>261828</v>
+        <v>6217498</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>9163478</v>
+        <v>244874</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>3687137</v>
+        <v>3051303</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>4875436</v>
+        <v>1866035</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>2881801</v>
+        <v>2204882</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>3933179</v>
+        <v>7212044</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>4764659</v>
+        <v>7818686</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5186202</v>
+        <v>428690</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>648760</v>
+        <v>4959858</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>6283005</v>
+        <v>4849325</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>2275393</v>
+        <v>961779</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>5081677</v>
+        <v>4176177</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>5624685</v>
+        <v>9450766</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>7045967</v>
+        <v>1277055</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>7131635</v>
+        <v>7263911</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>8391039</v>
+        <v>312047</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>2230968</v>
+        <v>6445810</v>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>7961001</v>
+        <v>2271103</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>7007306</v>
+        <v>526256</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>3664039</v>
+        <v>6558709</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>9042503</v>
+        <v>3603766</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>3178726</v>
+        <v>8834824</v>
       </c>
     </row>
     <row r="11">
@@ -1381,100 +1381,100 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2932025</v>
+        <v>9231395</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>7768759</v>
+        <v>9470693</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3788812</v>
+        <v>2142096</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7735456</v>
+        <v>1204057</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>8223388</v>
+        <v>7815018</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8926713</v>
+        <v>1230785</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2520424</v>
+        <v>7664463</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>8005053</v>
+        <v>9803964</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>7490065</v>
+        <v>3436962</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4540198</v>
+        <v>9389044</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3536632</v>
+        <v>5822803</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>380279</v>
+        <v>2564492</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>170908</v>
+        <v>9929199</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>6118376</v>
+        <v>3800501</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>9177571</v>
+        <v>9668271</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>3705960</v>
+        <v>7620034</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>1958608</v>
+        <v>821619</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>2775228</v>
+        <v>899005</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>6263636</v>
+        <v>8891406</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>1300434</v>
+        <v>6475296</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>5143553</v>
+        <v>7628412</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1707923</v>
+        <v>5243356</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>3533104</v>
+        <v>7766611</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>8726969</v>
+        <v>7668423</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>3327640</v>
+        <v>5776453</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>3445115</v>
+        <v>2447772</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>4968320</v>
+        <v>6362036</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>6968019</v>
+        <v>5203321</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>9265795</v>
+        <v>6984039</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>7107695</v>
+        <v>9542503</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>3985233</v>
+        <v>8131961</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>4989029</v>
+        <v>8974673</v>
       </c>
     </row>
     <row r="12">
@@ -1484,100 +1484,100 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9187108</v>
+        <v>3407306</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1684035</v>
+        <v>3908450</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1355034</v>
+        <v>8066729</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>9893863</v>
+        <v>9716364</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>68756</v>
+        <v>6370367</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4423271</v>
+        <v>5496381</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1643631</v>
+        <v>4797010</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1109759</v>
+        <v>1613065</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>4285043</v>
+        <v>8945018</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>7686030</v>
+        <v>5796027</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>6048275</v>
+        <v>8415086</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>8577312</v>
+        <v>6611901</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>4978313</v>
+        <v>7152801</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>859356</v>
+        <v>4899180</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9142906</v>
+        <v>5145691</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>6202324</v>
+        <v>9615130</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>5165050</v>
+        <v>2643701</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>1344778</v>
+        <v>4903738</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>9299068</v>
+        <v>5583567</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5133568</v>
+        <v>400725</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>2162618</v>
+        <v>975450</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>2694940</v>
+        <v>4336356</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2073414</v>
+        <v>8237370</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>8610126</v>
+        <v>328343</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>221368</v>
+        <v>3713676</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>7557343</v>
+        <v>6202209</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>7325223</v>
+        <v>9449473</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>634001</v>
+        <v>8213873</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>8508263</v>
+        <v>8463247</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>4336476</v>
+        <v>9631458</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>8204520</v>
+        <v>1653307</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>220347</v>
+        <v>9919856</v>
       </c>
     </row>
     <row r="13">
@@ -1587,100 +1587,100 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>6722905</v>
+        <v>299278</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2520337</v>
+        <v>5912078</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>996121</v>
+        <v>2186793</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1056127</v>
+        <v>838696</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>8978666</v>
+        <v>6891452</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3038552</v>
+        <v>6467998</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>5736476</v>
+        <v>4167757</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4594288</v>
+        <v>1162170</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6721783</v>
+        <v>3351979</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1779602</v>
+        <v>3420844</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>6073308</v>
+        <v>8700432</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>3273661</v>
+        <v>9640572</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>5482242</v>
+        <v>4048693</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>6922964</v>
+        <v>9902873</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>5791287</v>
+        <v>7485429</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>3894936</v>
+        <v>6806685</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>8174079</v>
+        <v>9619754</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1939610</v>
+        <v>7465019</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>191474</v>
+        <v>9500050</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>1453927</v>
+        <v>6188211</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>8927541</v>
+        <v>5658762</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>3644215</v>
+        <v>1282665</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>1022086</v>
+        <v>888623</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2506587</v>
+        <v>1482964</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>936101</v>
+        <v>7451083</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>4164573</v>
+        <v>9185471</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>5740423</v>
+        <v>8355012</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>19940</v>
+        <v>5035563</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>6327077</v>
+        <v>3412675</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>2759162</v>
+        <v>2522876</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>3464440</v>
+        <v>515609</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>8721086</v>
+        <v>1968755</v>
       </c>
     </row>
     <row r="14">
@@ -1690,100 +1690,100 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5418061</v>
+        <v>5958327</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8663928</v>
+        <v>8518219</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4263516</v>
+        <v>3304788</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3393030</v>
+        <v>8075550</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>8392250</v>
+        <v>7668938</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>3861089</v>
+        <v>9201573</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8799591</v>
+        <v>7356912</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2006575</v>
+        <v>5245258</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5516349</v>
+        <v>6335420</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>9861210</v>
+        <v>458465</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>2972759</v>
+        <v>2068698</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>7929902</v>
+        <v>3277474</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>6991112</v>
+        <v>4788328</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>3739198</v>
+        <v>2358486</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>869681</v>
+        <v>2050928</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>3495724</v>
+        <v>7391994</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>6257657</v>
+        <v>7557621</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>5297658</v>
+        <v>8231512</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>2859069</v>
+        <v>6228877</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>6416988</v>
+        <v>1206486</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>8962390</v>
+        <v>9814797</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>6417274</v>
+        <v>3784189</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>2894727</v>
+        <v>2890950</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>2011096</v>
+        <v>9979619</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>9320260</v>
+        <v>4676740</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>6882487</v>
+        <v>1098536</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>7734531</v>
+        <v>6158974</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>4716913</v>
+        <v>6343539</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>395667</v>
+        <v>2112416</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>2460369</v>
+        <v>9448913</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>3182507</v>
+        <v>2287838</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>8153449</v>
+        <v>6937808</v>
       </c>
     </row>
     <row r="15">
@@ -1793,100 +1793,100 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>215764</v>
+        <v>7408290</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>7150050</v>
+        <v>8351631</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3899889</v>
+        <v>9796194</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>4272542</v>
+        <v>7120937</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3807317</v>
+        <v>1381803</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>5171684</v>
+        <v>6011463</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>257370</v>
+        <v>9261303</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>6034146</v>
+        <v>9497261</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5992134</v>
+        <v>5064415</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8113553</v>
+        <v>9693479</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>3961115</v>
+        <v>1282538</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>4037655</v>
+        <v>1528447</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1599470</v>
+        <v>8611728</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>4558661</v>
+        <v>8823848</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>3031400</v>
+        <v>4286835</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>403390</v>
+        <v>2874900</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>1055820</v>
+        <v>9131022</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>1053172</v>
+        <v>9495003</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>9786085</v>
+        <v>9784613</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>2233833</v>
+        <v>7443527</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>759580</v>
+        <v>6682909</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>3394900</v>
+        <v>5312905</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>5362401</v>
+        <v>5689937</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>4841441</v>
+        <v>4416826</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>2483899</v>
+        <v>5053617</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>5705214</v>
+        <v>5963922</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>4539913</v>
+        <v>848417</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>2321999</v>
+        <v>6793136</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>2295926</v>
+        <v>6051786</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>6906244</v>
+        <v>8443608</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>2491110</v>
+        <v>811602</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>4824748</v>
+        <v>1334720</v>
       </c>
     </row>
     <row r="16">
@@ -1896,100 +1896,100 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>817351</v>
+        <v>5586563</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6438995</v>
+        <v>4683365</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4730883</v>
+        <v>5662068</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>8059108</v>
+        <v>9427507</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9174124</v>
+        <v>901851</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4793319</v>
+        <v>2514532</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2712722</v>
+        <v>188985</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8163027</v>
+        <v>5266428</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1593245</v>
+        <v>2303700</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>7638735</v>
+        <v>8557636</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3830266</v>
+        <v>6363443</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>9979828</v>
+        <v>3971856</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9679843</v>
+        <v>5294316</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9841596</v>
+        <v>2964509</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1037844</v>
+        <v>6701483</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>8920289</v>
+        <v>2179989</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>4735449</v>
+        <v>5658123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>5801915</v>
+        <v>2357734</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>861005</v>
+        <v>1849896</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>817534</v>
+        <v>829577</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>4856951</v>
+        <v>5637150</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>763730</v>
+        <v>6243534</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>7439865</v>
+        <v>6432068</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>43767</v>
+        <v>9435483</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4231115</v>
+        <v>7805027</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>1321263</v>
+        <v>8569471</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>5969941</v>
+        <v>7562838</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>6961535</v>
+        <v>7175505</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>7948995</v>
+        <v>1687137</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>3378018</v>
+        <v>6496285</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>7456562</v>
+        <v>9945508</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>590297</v>
+        <v>9377628</v>
       </c>
     </row>
     <row r="17">
@@ -1999,100 +1999,100 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5366138</v>
+        <v>3025939</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5325341</v>
+        <v>2118829</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6214134</v>
+        <v>390910</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9636328</v>
+        <v>1042522</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1934185</v>
+        <v>4209162</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>7827874</v>
+        <v>5883607</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>6575878</v>
+        <v>121415</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7820444</v>
+        <v>4399307</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5407568</v>
+        <v>7086451</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>2455370</v>
+        <v>6119644</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>7712535</v>
+        <v>321512</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1828119</v>
+        <v>5357823</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>7241141</v>
+        <v>1851044</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>543768</v>
+        <v>153524</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6993019</v>
+        <v>6272922</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>4596555</v>
+        <v>7266414</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>2258705</v>
+        <v>2112084</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>6758857</v>
+        <v>8308309</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>1109064</v>
+        <v>1502317</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>3280605</v>
+        <v>9656583</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>6792950</v>
+        <v>4306279</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>1936717</v>
+        <v>9251809</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>8126395</v>
+        <v>8977755</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>8115494</v>
+        <v>1305001</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>9436138</v>
+        <v>3110764</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>8334918</v>
+        <v>9952663</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>9131378</v>
+        <v>5132716</v>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>8840395</v>
+        <v>6981473</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>2384268</v>
+        <v>1601985</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>9399473</v>
+        <v>4378416</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>2720307</v>
+        <v>3548943</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>6092372</v>
+        <v>38503</v>
       </c>
     </row>
     <row r="18">
@@ -2102,100 +2102,100 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>7266918</v>
+        <v>7757002</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1182211</v>
+        <v>6284513</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5396133</v>
+        <v>2374821</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>4535278</v>
+        <v>3209145</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6990445</v>
+        <v>8401441</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2188153</v>
+        <v>7354567</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>6595579</v>
+        <v>4674427</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1436749</v>
+        <v>4897352</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>8844212</v>
+        <v>7931935</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>2058986</v>
+        <v>4985181</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>5886699</v>
+        <v>8810343</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>5251083</v>
+        <v>5243872</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>6397618</v>
+        <v>158908</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>8232326</v>
+        <v>2030418</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>3309766</v>
+        <v>4189320</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>9412693</v>
+        <v>1158839</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>4790648</v>
+        <v>5029866</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>5895319</v>
+        <v>1450726</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>4085670</v>
+        <v>1443993</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>2507413</v>
+        <v>1665229</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>4466439</v>
+        <v>9975812</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>6894198</v>
+        <v>1229813</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>2367319</v>
+        <v>9403073</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>7443113</v>
+        <v>7415489</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>4067805</v>
+        <v>6714618</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>800138</v>
+        <v>8039721</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>5672772</v>
+        <v>6566647</v>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>8250335</v>
+        <v>9095888</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>6441249</v>
+        <v>1687570</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>2069736</v>
+        <v>1653000</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>5773198</v>
+        <v>5158152</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>428472</v>
+        <v>7319729</v>
       </c>
     </row>
     <row r="19">
@@ -2205,100 +2205,100 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7531392</v>
+        <v>1837586</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>5800963</v>
+        <v>8292736</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3511817</v>
+        <v>6506344</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>3361966</v>
+        <v>4073810</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5101886</v>
+        <v>1777077</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2959111</v>
+        <v>7136454</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3670034</v>
+        <v>4394218</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4717023</v>
+        <v>428246</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>4265513</v>
+        <v>926385</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>7055491</v>
+        <v>3184588</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>4094068</v>
+        <v>3250165</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>7166614</v>
+        <v>8509337</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>5506066</v>
+        <v>4098398</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1576469</v>
+        <v>4400705</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>246541</v>
+        <v>6385656</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>9237187</v>
+        <v>7892094</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>9338994</v>
+        <v>6285243</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>4585256</v>
+        <v>1655941</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>2982857</v>
+        <v>416953</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>4821423</v>
+        <v>9545712</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>591386</v>
+        <v>9784587</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>6370439</v>
+        <v>3121781</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>9207764</v>
+        <v>1095634</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>4721303</v>
+        <v>9656909</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>2013021</v>
+        <v>8148959</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>9217226</v>
+        <v>5323953</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>1021307</v>
+        <v>9293879</v>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>2494739</v>
+        <v>1210809</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>7577628</v>
+        <v>3712975</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>97511</v>
+        <v>1917428</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>3365444</v>
+        <v>9174646</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>7775366</v>
+        <v>4693023</v>
       </c>
     </row>
     <row r="20">
@@ -2308,100 +2308,100 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2472321</v>
+        <v>5700121</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2731660</v>
+        <v>883976</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6906928</v>
+        <v>2352044</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5301512</v>
+        <v>198136</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7454263</v>
+        <v>6879194</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>377530</v>
+        <v>3518439</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1413575</v>
+        <v>7695460</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>8058277</v>
+        <v>2696929</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8249218</v>
+        <v>1325920</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>6070796</v>
+        <v>4930511</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>315608</v>
+        <v>1434651</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>4457392</v>
+        <v>8501857</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>7622544</v>
+        <v>4504809</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>6114360</v>
+        <v>5376741</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>7391693</v>
+        <v>8745512</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>3109711</v>
+        <v>449549</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2782744</v>
+        <v>5380183</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>6716404</v>
+        <v>308743</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>392781</v>
+        <v>6820325</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>3608574</v>
+        <v>4482050</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>6907607</v>
+        <v>7189354</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>7114197</v>
+        <v>1261595</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>4076114</v>
+        <v>1981028</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>2790942</v>
+        <v>5738411</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>8265131</v>
+        <v>4619629</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>534133</v>
+        <v>9672960</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>3443582</v>
+        <v>3035183</v>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>4213312</v>
+        <v>1496771</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>7885636</v>
+        <v>6555057</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>8837699</v>
+        <v>6535953</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>1172237</v>
+        <v>2987271</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>8496350</v>
+        <v>6983865</v>
       </c>
     </row>
     <row r="21">
@@ -2411,100 +2411,100 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>6490664</v>
+        <v>4196526</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3931331</v>
+        <v>6130552</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>4522892</v>
+        <v>6257956</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>4389692</v>
+        <v>8902854</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6114973</v>
+        <v>1234421</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3090040</v>
+        <v>3564833</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>937641</v>
+        <v>3752660</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>8425923</v>
+        <v>7821590</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3582333</v>
+        <v>7202790</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>9912727</v>
+        <v>7690420</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>2883592</v>
+        <v>5538321</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>6105979</v>
+        <v>8119013</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>3155879</v>
+        <v>3237265</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>7071302</v>
+        <v>9754202</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6365769</v>
+        <v>6291631</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>9797251</v>
+        <v>958691</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>6617853</v>
+        <v>77694</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>9260353</v>
+        <v>293086</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>9658845</v>
+        <v>4894627</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>3128782</v>
+        <v>8116674</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>3212784</v>
+        <v>6819441</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>6427869</v>
+        <v>8060775</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2711531</v>
+        <v>318189</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>577379</v>
+        <v>1709886</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>2379010</v>
+        <v>8071574</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>8757215</v>
+        <v>2461317</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>5844193</v>
+        <v>216234</v>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>4275115</v>
+        <v>8758430</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>4667936</v>
+        <v>365377</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>4342229</v>
+        <v>7314751</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>9112136</v>
+        <v>4801998</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>2782597</v>
+        <v>1745333</v>
       </c>
     </row>
     <row r="22">
@@ -2514,100 +2514,100 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>3297277</v>
+        <v>7957468</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6560303</v>
+        <v>3099651</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2549395</v>
+        <v>4234081</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>4160381</v>
+        <v>486279</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5383878</v>
+        <v>6184853</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9200985</v>
+        <v>5660677</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>5105013</v>
+        <v>7549245</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>7510369</v>
+        <v>4772240</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>6977960</v>
+        <v>9878928</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>7117631</v>
+        <v>4320276</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>9774129</v>
+        <v>4328350</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>7264342</v>
+        <v>4968623</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>5713343</v>
+        <v>9891157</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9068050</v>
+        <v>6484641</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>5676920</v>
+        <v>662577</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>1855291</v>
+        <v>1485593</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>7101688</v>
+        <v>6186855</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>908774</v>
+        <v>4241130</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>1880025</v>
+        <v>5448524</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>8974975</v>
+        <v>4698155</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>4052308</v>
+        <v>952582</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>9302095</v>
+        <v>811043</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>1910945</v>
+        <v>2555384</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>5432768</v>
+        <v>1115620</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>6115779</v>
+        <v>375476</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>5342268</v>
+        <v>3453049</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>2564642</v>
+        <v>5615010</v>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>7327449</v>
+        <v>3954914</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>5945045</v>
+        <v>1868773</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>8813969</v>
+        <v>4724060</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>680249</v>
+        <v>5102294</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>4708670</v>
+        <v>9998615</v>
       </c>
     </row>
     <row r="23">
@@ -2617,100 +2617,100 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3538060</v>
+        <v>9958566</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5199020</v>
+        <v>7303459</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>8592378</v>
+        <v>2944237</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6925261</v>
+        <v>9438603</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4178199</v>
+        <v>9409593</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2802104</v>
+        <v>9725326</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7716084</v>
+        <v>1717148</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8637378</v>
+        <v>3585816</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5696336</v>
+        <v>9623973</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>537695</v>
+        <v>4806356</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>6136177</v>
+        <v>5181610</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>6837193</v>
+        <v>5936636</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3461767</v>
+        <v>2708395</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>6342233</v>
+        <v>7621478</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>69219</v>
+        <v>7314527</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4971195</v>
+        <v>4611754</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1102785</v>
+        <v>4679937</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1228624</v>
+        <v>7026014</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>3251627</v>
+        <v>5016693</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>4296298</v>
+        <v>1350470</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>4694023</v>
+        <v>4790146</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>8519475</v>
+        <v>2768691</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>4997862</v>
+        <v>4397470</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9560393</v>
+        <v>4918826</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>7638231</v>
+        <v>6973287</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>1399497</v>
+        <v>440667</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>7795914</v>
+        <v>9319169</v>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>9875528</v>
+        <v>9912337</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>6898304</v>
+        <v>8351320</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>6963011</v>
+        <v>3972341</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>6391235</v>
+        <v>3293540</v>
       </c>
       <c r="AG23" s="3" t="n">
-        <v>1849340</v>
+        <v>4709700</v>
       </c>
     </row>
     <row r="24">
@@ -2720,100 +2720,100 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4014034</v>
+        <v>3922538</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1716910</v>
+        <v>9871961</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>6907990</v>
+        <v>9618232</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9582724</v>
+        <v>4913727</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>7085749</v>
+        <v>5514293</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>5847689</v>
+        <v>6884708</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>3341320</v>
+        <v>1204100</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>3410281</v>
+        <v>3151348</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>6018303</v>
+        <v>7071121</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>4069415</v>
+        <v>2675074</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1255983</v>
+        <v>1610478</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>5013284</v>
+        <v>6785928</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2711176</v>
+        <v>6716129</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>7487928</v>
+        <v>7455890</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>87377</v>
+        <v>9578881</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>6389076</v>
+        <v>7460052</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>9153347</v>
+        <v>7257263</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>5302074</v>
+        <v>8803884</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>2809583</v>
+        <v>169142</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>5748072</v>
+        <v>9234681</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>8179769</v>
+        <v>2298337</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>9689716</v>
+        <v>5049493</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>2200695</v>
+        <v>4439894</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>7966999</v>
+        <v>5852666</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>727575</v>
+        <v>7198505</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>28433</v>
+        <v>9685183</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>8319717</v>
+        <v>731197</v>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>1221917</v>
+        <v>9223523</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>6697709</v>
+        <v>9944794</v>
       </c>
       <c r="AE24" s="3" t="n">
-        <v>7137512</v>
+        <v>6908649</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>9128652</v>
+        <v>9565028</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>9894302</v>
+        <v>592738</v>
       </c>
     </row>
     <row r="25">
@@ -2823,100 +2823,100 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8197973</v>
+        <v>8680157</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>9594332</v>
+        <v>9205192</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>197853</v>
+        <v>1175519</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>11748</v>
+        <v>6334796</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4541820</v>
+        <v>342175</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>7523314</v>
+        <v>1786284</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>9431495</v>
+        <v>4449431</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4457499</v>
+        <v>8435518</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>6662738</v>
+        <v>2166448</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>183547</v>
+        <v>7434303</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>7008007</v>
+        <v>3293981</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>612754</v>
+        <v>3180173</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>9202587</v>
+        <v>8758659</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>5391070</v>
+        <v>6893331</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>3580297</v>
+        <v>4781294</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>3977003</v>
+        <v>5159089</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>1486843</v>
+        <v>5408765</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>3443694</v>
+        <v>3557480</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>9377336</v>
+        <v>4970050</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>4998698</v>
+        <v>6161420</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>8169275</v>
+        <v>5601031</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>4469929</v>
+        <v>3099934</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>2050443</v>
+        <v>94231</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>6910176</v>
+        <v>3056926</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>9363112</v>
+        <v>5017467</v>
       </c>
       <c r="AA25" s="3" t="n">
-        <v>8015349</v>
+        <v>9349973</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>5350324</v>
+        <v>2485092</v>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>3125560</v>
+        <v>3889298</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>4971727</v>
+        <v>5178194</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>8776841</v>
+        <v>2831294</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>3243412</v>
+        <v>3561664</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>5298514</v>
+        <v>5983311</v>
       </c>
     </row>
     <row r="26">
@@ -2926,100 +2926,100 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>4591884</v>
+        <v>929509</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>6667729</v>
+        <v>3129254</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>4980736</v>
+        <v>5543367</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1166026</v>
+        <v>3647060</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5581188</v>
+        <v>9658743</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>6069960</v>
+        <v>262954</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6757123</v>
+        <v>5259193</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>6908825</v>
+        <v>7321625</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>209521</v>
+        <v>5454030</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>184776</v>
+        <v>9936254</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>9314412</v>
+        <v>3932016</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>3747363</v>
+        <v>1122978</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>7782352</v>
+        <v>6843069</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>9904456</v>
+        <v>8263059</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>113635</v>
+        <v>243444</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>9119058</v>
+        <v>4470473</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>6382269</v>
+        <v>4753884</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>3080347</v>
+        <v>4347257</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>2260284</v>
+        <v>9372753</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>5254140</v>
+        <v>93815</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>386132</v>
+        <v>2178473</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>1153529</v>
+        <v>8909143</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>6563430</v>
+        <v>2377579</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>7344279</v>
+        <v>9098329</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>657927</v>
+        <v>2470095</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>623266</v>
+        <v>9852912</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>5736536</v>
+        <v>4605332</v>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>7520733</v>
+        <v>2767547</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>7757088</v>
+        <v>4801857</v>
       </c>
       <c r="AE26" s="3" t="n">
-        <v>541181</v>
+        <v>2624088</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>7866812</v>
+        <v>2513175</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>7867488</v>
+        <v>1027676</v>
       </c>
     </row>
     <row r="27">
@@ -3029,100 +3029,100 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3413511</v>
+        <v>6413504</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7440432</v>
+        <v>1383314</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>178274</v>
+        <v>9312188</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>8673188</v>
+        <v>2443712</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7090170</v>
+        <v>8793423</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4162819</v>
+        <v>1548662</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5494036</v>
+        <v>8473061</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>8437430</v>
+        <v>2049798</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8067415</v>
+        <v>4927148</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7016053</v>
+        <v>1402016</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1007007</v>
+        <v>4910123</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>5783053</v>
+        <v>8082339</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>5694419</v>
+        <v>2423857</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>5193650</v>
+        <v>463737</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9747853</v>
+        <v>2563974</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3600950</v>
+        <v>4268999</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>3749744</v>
+        <v>5317891</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>8517203</v>
+        <v>4632291</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>9556693</v>
+        <v>1904209</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>8088278</v>
+        <v>6614851</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>3738528</v>
+        <v>3737070</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>4789959</v>
+        <v>6637492</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>4339377</v>
+        <v>2296605</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>6962957</v>
+        <v>5763648</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>4283225</v>
+        <v>6519391</v>
       </c>
       <c r="AA27" s="3" t="n">
-        <v>9359690</v>
+        <v>8822183</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>2229794</v>
+        <v>98522</v>
       </c>
       <c r="AC27" s="3" t="n">
-        <v>3174108</v>
+        <v>2296606</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>8637940</v>
+        <v>2290359</v>
       </c>
       <c r="AE27" s="3" t="n">
-        <v>3542751</v>
+        <v>5666833</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>3624257</v>
+        <v>7184915</v>
       </c>
       <c r="AG27" s="3" t="n">
-        <v>5517758</v>
+        <v>5312079</v>
       </c>
     </row>
     <row r="28">
@@ -3132,100 +3132,100 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>4257868</v>
+        <v>2917176</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5663119</v>
+        <v>1512537</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2098849</v>
+        <v>1006682</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1366594</v>
+        <v>8459373</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>234841</v>
+        <v>327140</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9703918</v>
+        <v>4659659</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>6619760</v>
+        <v>4028510</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3288057</v>
+        <v>2976695</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3028240</v>
+        <v>5801636</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1972066</v>
+        <v>1879858</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>7896464</v>
+        <v>8678565</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1125020</v>
+        <v>7066812</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>5874061</v>
+        <v>5168198</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1572391</v>
+        <v>6893147</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>4034002</v>
+        <v>3705974</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>5265483</v>
+        <v>783691</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>7850622</v>
+        <v>6685077</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2141500</v>
+        <v>175724</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>7962206</v>
+        <v>7721363</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8741262</v>
+        <v>2114278</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>9902934</v>
+        <v>8690345</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>8224099</v>
+        <v>1092465</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>8592415</v>
+        <v>1806891</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>1454811</v>
+        <v>9321905</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2694918</v>
+        <v>1775937</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>6748148</v>
+        <v>3693028</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>1436447</v>
+        <v>4940938</v>
       </c>
       <c r="AC28" s="3" t="n">
-        <v>1104662</v>
+        <v>491703</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>5025451</v>
+        <v>2874816</v>
       </c>
       <c r="AE28" s="3" t="n">
-        <v>928458</v>
+        <v>8851664</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>8004193</v>
+        <v>3803230</v>
       </c>
       <c r="AG28" s="3" t="n">
-        <v>7856437</v>
+        <v>6187995</v>
       </c>
     </row>
     <row r="29">
@@ -3235,100 +3235,100 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2480658</v>
+        <v>9314248</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5446483</v>
+        <v>6279843</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7855614</v>
+        <v>6352742</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7701819</v>
+        <v>4597280</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7726002</v>
+        <v>2090193</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1676920</v>
+        <v>1022094</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>186594</v>
+        <v>7287943</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1772346</v>
+        <v>944455</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>255282</v>
+        <v>5789936</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3632963</v>
+        <v>2239532</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6023279</v>
+        <v>1759517</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>4133185</v>
+        <v>9618355</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>574113</v>
+        <v>2084362</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4054804</v>
+        <v>2133127</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6998291</v>
+        <v>2375800</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>547485</v>
+        <v>7534528</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>9919575</v>
+        <v>1392451</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>2043073</v>
+        <v>7903840</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>3740865</v>
+        <v>5619609</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>5218642</v>
+        <v>6523987</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>7972718</v>
+        <v>4496036</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>9394633</v>
+        <v>1808435</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>4895501</v>
+        <v>1844732</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>557875</v>
+        <v>6381846</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>4568171</v>
+        <v>6845406</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>5282498</v>
+        <v>7211729</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>4401156</v>
+        <v>4850963</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>7368648</v>
+        <v>4850056</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>3988801</v>
+        <v>7410817</v>
       </c>
       <c r="AE29" s="3" t="n">
-        <v>8488382</v>
+        <v>6627716</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>1772852</v>
+        <v>4741637</v>
       </c>
       <c r="AG29" s="3" t="n">
-        <v>7024944</v>
+        <v>2663100</v>
       </c>
     </row>
     <row r="30">
@@ -3338,100 +3338,100 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9985698</v>
+        <v>9182466</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5288057</v>
+        <v>886431</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4395624</v>
+        <v>6209678</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8202083</v>
+        <v>1222253</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3265818</v>
+        <v>4869915</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5241586</v>
+        <v>1690718</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7183042</v>
+        <v>4987613</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>7288277</v>
+        <v>6961683</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1289310</v>
+        <v>509218</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>9483556</v>
+        <v>1988976</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>6032434</v>
+        <v>8499012</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>5901510</v>
+        <v>8518330</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6187715</v>
+        <v>7501560</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>4842947</v>
+        <v>6185669</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1286883</v>
+        <v>1897485</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1031577</v>
+        <v>1179597</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9208747</v>
+        <v>3210770</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>692635</v>
+        <v>3855637</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8601654</v>
+        <v>4655039</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>3557515</v>
+        <v>8875774</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>3290557</v>
+        <v>3353584</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>2213215</v>
+        <v>5841695</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>9238779</v>
+        <v>781670</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>4604464</v>
+        <v>6422559</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>7673381</v>
+        <v>343737</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>8007828</v>
+        <v>7425457</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>7517079</v>
+        <v>5191686</v>
       </c>
       <c r="AC30" s="3" t="n">
-        <v>584732</v>
+        <v>391392</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>7835256</v>
+        <v>2664175</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>8946096</v>
+        <v>8216205</v>
       </c>
       <c r="AF30" s="3" t="n">
-        <v>5874836</v>
+        <v>8747829</v>
       </c>
       <c r="AG30" s="3" t="n">
-        <v>1443484</v>
+        <v>8950621</v>
       </c>
     </row>
     <row r="31">
@@ -3441,100 +3441,100 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>6149155</v>
+        <v>4462358</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>5602101</v>
+        <v>9425047</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3995147</v>
+        <v>1694310</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2054729</v>
+        <v>1440123</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>663614</v>
+        <v>8855279</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>9002691</v>
+        <v>7750995</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>7230052</v>
+        <v>6765519</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7952385</v>
+        <v>8318261</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2392519</v>
+        <v>8215952</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>3886348</v>
+        <v>5211005</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>4411520</v>
+        <v>4345615</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>9117201</v>
+        <v>982915</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8998688</v>
+        <v>9660680</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1398291</v>
+        <v>2297037</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>7250488</v>
+        <v>2574228</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>1518666</v>
+        <v>871072</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>7598552</v>
+        <v>7529072</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>3355762</v>
+        <v>8579798</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>8093138</v>
+        <v>349313</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>7739272</v>
+        <v>7212583</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>3701057</v>
+        <v>6626385</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>8017114</v>
+        <v>6867918</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>9464763</v>
+        <v>4873960</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2221924</v>
+        <v>843463</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>9970791</v>
+        <v>5074239</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>4207937</v>
+        <v>153964</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>7590846</v>
+        <v>3470689</v>
       </c>
       <c r="AC31" s="3" t="n">
-        <v>567904</v>
+        <v>6227323</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>4740194</v>
+        <v>5044932</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>4467667</v>
+        <v>6331409</v>
       </c>
       <c r="AF31" s="3" t="n">
-        <v>5998517</v>
+        <v>2347117</v>
       </c>
       <c r="AG31" s="3" t="n">
-        <v>4006574</v>
+        <v>3802804</v>
       </c>
     </row>
     <row r="32">
@@ -3544,100 +3544,100 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>4056746</v>
+        <v>906488</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1682524</v>
+        <v>7476789</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>951637</v>
+        <v>5607679</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5203582</v>
+        <v>6009499</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>6700098</v>
+        <v>3397069</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>7701524</v>
+        <v>7481880</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>234928</v>
+        <v>575390</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8036594</v>
+        <v>6124381</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>4480942</v>
+        <v>5498236</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>6389778</v>
+        <v>3440994</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>147473</v>
+        <v>8088713</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>6022215</v>
+        <v>4709920</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>7628623</v>
+        <v>2808543</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>3088390</v>
+        <v>76610</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>604133</v>
+        <v>9925869</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>3430407</v>
+        <v>3532413</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>7938665</v>
+        <v>84688</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>6986307</v>
+        <v>1540388</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3407618</v>
+        <v>4229805</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>562593</v>
+        <v>6728281</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>5389565</v>
+        <v>2559942</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>6335345</v>
+        <v>3192620</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>2257748</v>
+        <v>4973255</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>7974348</v>
+        <v>115712</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>6496474</v>
+        <v>2641410</v>
       </c>
       <c r="AA32" s="3" t="n">
-        <v>4967298</v>
+        <v>5447680</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>744511</v>
+        <v>1955728</v>
       </c>
       <c r="AC32" s="3" t="n">
-        <v>5757140</v>
+        <v>1493079</v>
       </c>
       <c r="AD32" s="3" t="n">
-        <v>9584358</v>
+        <v>1278605</v>
       </c>
       <c r="AE32" s="3" t="n">
-        <v>6084183</v>
+        <v>8548732</v>
       </c>
       <c r="AF32" s="3" t="n">
-        <v>6858109</v>
+        <v>388063</v>
       </c>
       <c r="AG32" s="3" t="n">
-        <v>8091553</v>
+        <v>4256131</v>
       </c>
     </row>
     <row r="33">
@@ -3647,100 +3647,100 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2724395</v>
+        <v>8452746</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>4452070</v>
+        <v>5162456</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2886917</v>
+        <v>9614497</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>8418977</v>
+        <v>6499762</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>5851715</v>
+        <v>153995</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>7302006</v>
+        <v>9233076</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2265005</v>
+        <v>8071506</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1912809</v>
+        <v>1704223</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>122752</v>
+        <v>6772898</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>3323520</v>
+        <v>7265578</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2432327</v>
+        <v>2317365</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>4531469</v>
+        <v>2835206</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>6626991</v>
+        <v>1344826</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>6892124</v>
+        <v>6775552</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4951241</v>
+        <v>5387959</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>4709778</v>
+        <v>8861197</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>9416472</v>
+        <v>9157551</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>9047442</v>
+        <v>9559463</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>3059666</v>
+        <v>4350698</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>1580019</v>
+        <v>1654637</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>2172404</v>
+        <v>1427117</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>2432567</v>
+        <v>911572</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>7977732</v>
+        <v>8285876</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1759053</v>
+        <v>3751543</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4541763</v>
+        <v>8327541</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>2703314</v>
+        <v>8506904</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>7018109</v>
+        <v>4833553</v>
       </c>
       <c r="AC33" s="3" t="n">
-        <v>3682117</v>
+        <v>7165441</v>
       </c>
       <c r="AD33" s="3" t="n">
-        <v>9608627</v>
+        <v>8255609</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>2630492</v>
+        <v>5339585</v>
       </c>
       <c r="AF33" s="3" t="n">
-        <v>2031291</v>
+        <v>3407751</v>
       </c>
       <c r="AG33" s="3" t="n">
-        <v>8779403</v>
+        <v>2607238</v>
       </c>
     </row>
     <row r="34">
@@ -3750,100 +3750,100 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>7035305</v>
+        <v>2970937</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2006654</v>
+        <v>6921175</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>421030</v>
+        <v>7012478</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>6059911</v>
+        <v>5609265</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1554762</v>
+        <v>5987226</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3743686</v>
+        <v>4531248</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>860308</v>
+        <v>516487</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>4728277</v>
+        <v>8047869</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3090482</v>
+        <v>8580118</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3213004</v>
+        <v>5195642</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>4523121</v>
+        <v>6231766</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>9662519</v>
+        <v>6885467</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>7391838</v>
+        <v>4593393</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>7692631</v>
+        <v>8123968</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>91761</v>
+        <v>601839</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>6300595</v>
+        <v>3884072</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>7313221</v>
+        <v>1051730</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>8651301</v>
+        <v>8346788</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>4215614</v>
+        <v>6760085</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>4501653</v>
+        <v>1400071</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>6726886</v>
+        <v>2093141</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>3305415</v>
+        <v>2726765</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>2834034</v>
+        <v>3537643</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>7829888</v>
+        <v>9823822</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8972518</v>
+        <v>8967709</v>
       </c>
       <c r="AA34" s="3" t="n">
-        <v>1866139</v>
+        <v>31714</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>6584085</v>
+        <v>3244541</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>8970100</v>
+        <v>3348918</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>1500809</v>
+        <v>5895421</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>677788</v>
+        <v>1403360</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>2420699</v>
+        <v>5724644</v>
       </c>
       <c r="AG34" s="3" t="n">
-        <v>6468364</v>
+        <v>2710856</v>
       </c>
     </row>
     <row r="35">
@@ -3853,100 +3853,100 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7517100</v>
+        <v>2370753</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>9886804</v>
+        <v>5172890</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>3570714</v>
+        <v>9517861</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>6828904</v>
+        <v>5174070</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>8900332</v>
+        <v>9636405</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2702144</v>
+        <v>6468351</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>8787399</v>
+        <v>7180593</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3457931</v>
+        <v>3879617</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>8191887</v>
+        <v>8126096</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>2673346</v>
+        <v>1572326</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>5329804</v>
+        <v>3318356</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>4739628</v>
+        <v>2153671</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1002256</v>
+        <v>6616322</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>4736284</v>
+        <v>559781</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>5519134</v>
+        <v>9973873</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>1245382</v>
+        <v>4257708</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>4262241</v>
+        <v>6757931</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>9323176</v>
+        <v>605853</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>9158329</v>
+        <v>9400470</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>4066155</v>
+        <v>5731228</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>7390558</v>
+        <v>4011923</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>5512916</v>
+        <v>3411989</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>4865240</v>
+        <v>4336577</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>6806643</v>
+        <v>443010</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>1045502</v>
+        <v>7667771</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>6496843</v>
+        <v>9073846</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>5121826</v>
+        <v>4141360</v>
       </c>
       <c r="AC35" s="3" t="n">
-        <v>5934697</v>
+        <v>389653</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>2870719</v>
+        <v>1874258</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>9642571</v>
+        <v>4130141</v>
       </c>
       <c r="AF35" s="3" t="n">
-        <v>1845775</v>
+        <v>9292099</v>
       </c>
       <c r="AG35" s="3" t="n">
-        <v>883885</v>
+        <v>7207482</v>
       </c>
     </row>
   </sheetData>
@@ -4177,100 +4177,100 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9358593</v>
+        <v>9602079</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7055012</v>
+        <v>7281529</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>9199276</v>
+        <v>6486852</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1704343</v>
+        <v>87119</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1947814</v>
+        <v>2638479</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>7896670</v>
+        <v>4945220</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5172011</v>
+        <v>2533539</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6593836</v>
+        <v>4778748</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1454216</v>
+        <v>7233431</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>581148</v>
+        <v>7989504</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5667940</v>
+        <v>5437588</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>7026997</v>
+        <v>8562977</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>6721922</v>
+        <v>6328393</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>7543502</v>
+        <v>7303165</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>7235594</v>
+        <v>9210252</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>5472791</v>
+        <v>3351718</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>4133629</v>
+        <v>3233764</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>7548901</v>
+        <v>3228581</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1723921</v>
+        <v>9349306</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>5859264</v>
+        <v>3827758</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>4388076</v>
+        <v>9690362</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1489976</v>
+        <v>8721803</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>9279128</v>
+        <v>3430143</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>8373422</v>
+        <v>5217219</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>4503027</v>
+        <v>3653466</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>3298</v>
+        <v>9871286</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>5971805</v>
+        <v>3146592</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>9181460</v>
+        <v>9879459</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>7693029</v>
+        <v>3478188</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1400855</v>
+        <v>9435582</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>827759</v>
+        <v>3873063</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>6617053</v>
+        <v>7632991</v>
       </c>
     </row>
     <row r="5">
@@ -4280,100 +4280,100 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5658005</v>
+        <v>9608181</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1991772</v>
+        <v>2456550</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4843109</v>
+        <v>819768</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3545638</v>
+        <v>8319375</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8525798</v>
+        <v>6155589</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>7659165</v>
+        <v>8310952</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>4102614</v>
+        <v>6709250</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>8942815</v>
+        <v>670103</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3886826</v>
+        <v>5765474</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>796106</v>
+        <v>3087408</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>8523433</v>
+        <v>7168661</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>7956683</v>
+        <v>7553464</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>6087722</v>
+        <v>4727910</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>2576076</v>
+        <v>3551550</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2077465</v>
+        <v>9316174</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1639586</v>
+        <v>3764542</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2344389</v>
+        <v>9767326</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>5656199</v>
+        <v>7590955</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>8887706</v>
+        <v>5096234</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>1973594</v>
+        <v>6279559</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>8440210</v>
+        <v>3360191</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>6457257</v>
+        <v>1484309</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>6725708</v>
+        <v>6731748</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7478441</v>
+        <v>7149653</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>5493956</v>
+        <v>747641</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>7653033</v>
+        <v>3868536</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>27668</v>
+        <v>2755228</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>5250859</v>
+        <v>8560133</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>6762903</v>
+        <v>9463309</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>533381</v>
+        <v>8294060</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>5857263</v>
+        <v>8088193</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1835793</v>
+        <v>9595324</v>
       </c>
     </row>
     <row r="6">
@@ -4383,100 +4383,100 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>629749</v>
+        <v>7822691</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7795563</v>
+        <v>8721237</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2667893</v>
+        <v>9782108</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>8102928</v>
+        <v>1593868</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2899909</v>
+        <v>1806058</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1013118</v>
+        <v>6636455</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1832295</v>
+        <v>6094433</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8150761</v>
+        <v>9250238</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>8483721</v>
+        <v>7615663</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>3180698</v>
+        <v>6790887</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>7281301</v>
+        <v>9519943</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>5074339</v>
+        <v>3056996</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>9544116</v>
+        <v>6592347</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>2598352</v>
+        <v>4271473</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>507451</v>
+        <v>8992376</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>3511496</v>
+        <v>5544466</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>9058739</v>
+        <v>7221324</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>182739</v>
+        <v>7467877</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>8647337</v>
+        <v>8671208</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>9594987</v>
+        <v>9000380</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>9800604</v>
+        <v>2067712</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>9810731</v>
+        <v>5841588</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>1893239</v>
+        <v>9802821</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>2957371</v>
+        <v>3943748</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>7749082</v>
+        <v>9620418</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>8641770</v>
+        <v>1524936</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>9371855</v>
+        <v>8621705</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>564490</v>
+        <v>6783080</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>9808540</v>
+        <v>825583</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>3841419</v>
+        <v>5546574</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>6121512</v>
+        <v>7290592</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>7384618</v>
+        <v>7948829</v>
       </c>
     </row>
     <row r="7">
@@ -4486,100 +4486,100 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>19824</v>
+        <v>315288</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9177583</v>
+        <v>9146337</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>593390</v>
+        <v>36425</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7878321</v>
+        <v>4183857</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4941413</v>
+        <v>6950522</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>5699771</v>
+        <v>9781582</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4212901</v>
+        <v>7503537</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1252643</v>
+        <v>8996260</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1990572</v>
+        <v>8436613</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>6687035</v>
+        <v>9452880</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>7037605</v>
+        <v>6516297</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>6242513</v>
+        <v>8924512</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>3070114</v>
+        <v>9210532</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>8671212</v>
+        <v>8680545</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>7069085</v>
+        <v>1620462</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>790733</v>
+        <v>1938</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>7845292</v>
+        <v>9185394</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>7503052</v>
+        <v>6335713</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>7886752</v>
+        <v>7811410</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>7521952</v>
+        <v>4859509</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>3976757</v>
+        <v>523975</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>8256960</v>
+        <v>6281307</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>281763</v>
+        <v>9382753</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>8430220</v>
+        <v>5043796</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>5447046</v>
+        <v>248902</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>1341243</v>
+        <v>1833120</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>4843468</v>
+        <v>1482597</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>2493576</v>
+        <v>6897975</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>6343745</v>
+        <v>1880247</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>3869466</v>
+        <v>1109872</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>9110541</v>
+        <v>7062284</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>2756041</v>
+        <v>3084112</v>
       </c>
     </row>
     <row r="8">
@@ -4589,100 +4589,100 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4649091</v>
+        <v>2762408</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7095482</v>
+        <v>2368450</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2892853</v>
+        <v>7821966</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7604704</v>
+        <v>6736140</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3504818</v>
+        <v>3409822</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3183254</v>
+        <v>40837</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>4726142</v>
+        <v>9741202</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8058708</v>
+        <v>2416759</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>608081</v>
+        <v>5868496</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>5369098</v>
+        <v>636567</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>2599209</v>
+        <v>8232720</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2777063</v>
+        <v>2686316</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>324523</v>
+        <v>6471762</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>6805389</v>
+        <v>9847325</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>7826197</v>
+        <v>4674330</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>9519008</v>
+        <v>3491645</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>5531744</v>
+        <v>642805</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>2422224</v>
+        <v>2291183</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>4927421</v>
+        <v>4878047</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>5127191</v>
+        <v>952564</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>8714218</v>
+        <v>1108194</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>8322960</v>
+        <v>5792663</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>4928402</v>
+        <v>4124032</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>8410686</v>
+        <v>5539454</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2219311</v>
+        <v>560285</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>6345492</v>
+        <v>1538425</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>768327</v>
+        <v>7644409</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>2283237</v>
+        <v>2719289</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>5708374</v>
+        <v>3546027</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>8608961</v>
+        <v>2571628</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>891133</v>
+        <v>4579290</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>250261</v>
+        <v>8431857</v>
       </c>
     </row>
     <row r="9">
@@ -4692,100 +4692,100 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2111463</v>
+        <v>3227522</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1236791</v>
+        <v>4786129</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4235832</v>
+        <v>3731789</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7716486</v>
+        <v>7981723</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3404311</v>
+        <v>8995821</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4610593</v>
+        <v>6708710</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8066210</v>
+        <v>1871405</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1355197</v>
+        <v>6700488</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>6775231</v>
+        <v>691375</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2159076</v>
+        <v>4569859</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>745250</v>
+        <v>7583770</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>9089011</v>
+        <v>7467274</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8147315</v>
+        <v>7588521</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1331144</v>
+        <v>2663831</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>9272001</v>
+        <v>7244732</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1037608</v>
+        <v>2009341</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>6616963</v>
+        <v>8703893</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>2166413</v>
+        <v>7286190</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3545847</v>
+        <v>5407117</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>8444564</v>
+        <v>9966532</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>7841838</v>
+        <v>7766700</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>5617392</v>
+        <v>3470726</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>7773793</v>
+        <v>9183744</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1686013</v>
+        <v>4137912</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>3742379</v>
+        <v>9579357</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>1883854</v>
+        <v>3263486</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>4640541</v>
+        <v>7622075</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>8779153</v>
+        <v>2317693</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>7359372</v>
+        <v>9711357</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>6567186</v>
+        <v>5653891</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>2500410</v>
+        <v>6816232</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>937296</v>
+        <v>1105501</v>
       </c>
     </row>
     <row r="10">
@@ -4795,100 +4795,100 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7485980</v>
+        <v>6022076</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6989259</v>
+        <v>6465922</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1066730</v>
+        <v>7723946</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5737399</v>
+        <v>5381559</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8249517</v>
+        <v>2945634</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>7832118</v>
+        <v>1715773</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7630707</v>
+        <v>1018556</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>5535119</v>
+        <v>8266739</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2124253</v>
+        <v>8579189</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1487861</v>
+        <v>4308885</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2098386</v>
+        <v>8977408</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>5380091</v>
+        <v>4449658</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>387156</v>
+        <v>2187499</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2793633</v>
+        <v>4772947</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7854254</v>
+        <v>3124082</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>9506021</v>
+        <v>9134389</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>3266619</v>
+        <v>9246804</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>4081651</v>
+        <v>2815723</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>8623111</v>
+        <v>3314382</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>9091689</v>
+        <v>2916861</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>8953768</v>
+        <v>8971214</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>4494277</v>
+        <v>5405913</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>6611923</v>
+        <v>3091286</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>4919702</v>
+        <v>3283054</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>4433414</v>
+        <v>3644123</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>9133071</v>
+        <v>9723608</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>9643546</v>
+        <v>6459178</v>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>3670412</v>
+        <v>13697</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>5213662</v>
+        <v>3496883</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>9072229</v>
+        <v>2259171</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>206230</v>
+        <v>5290453</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>4590123</v>
+        <v>1438593</v>
       </c>
     </row>
     <row r="11">
@@ -4898,100 +4898,100 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5662379</v>
+        <v>5911925</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9802572</v>
+        <v>9155076</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7365262</v>
+        <v>2491454</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6973674</v>
+        <v>4602567</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6826706</v>
+        <v>2042394</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7066971</v>
+        <v>4759071</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>9025771</v>
+        <v>9160769</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>6935818</v>
+        <v>9163284</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6105806</v>
+        <v>2497150</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>6385798</v>
+        <v>1735578</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3493359</v>
+        <v>7287993</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>7785724</v>
+        <v>3137270</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>9557473</v>
+        <v>1806287</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>8749256</v>
+        <v>165779</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1513598</v>
+        <v>452031</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6934606</v>
+        <v>6656811</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>2401633</v>
+        <v>9989970</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>7448935</v>
+        <v>5237233</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>8052577</v>
+        <v>4663667</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>618664</v>
+        <v>4886125</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>4621443</v>
+        <v>6247950</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>9541846</v>
+        <v>3858721</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>4629888</v>
+        <v>9075000</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>6291398</v>
+        <v>9754900</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>8418117</v>
+        <v>4776800</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>1919528</v>
+        <v>4023057</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>5516196</v>
+        <v>6164517</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>1088824</v>
+        <v>939777</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>478024</v>
+        <v>1391116</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>3232048</v>
+        <v>5898920</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>6754439</v>
+        <v>1840499</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>1094405</v>
+        <v>7020778</v>
       </c>
     </row>
     <row r="12">
@@ -5001,100 +5001,100 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6228474</v>
+        <v>697722</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4092780</v>
+        <v>3654748</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5913572</v>
+        <v>2512530</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5114136</v>
+        <v>6763606</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>8566987</v>
+        <v>4746996</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3212392</v>
+        <v>4310457</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>6822234</v>
+        <v>7319895</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1796210</v>
+        <v>5088125</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5188048</v>
+        <v>8727030</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2091989</v>
+        <v>869750</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>7642613</v>
+        <v>7164705</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1429684</v>
+        <v>5102315</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2142196</v>
+        <v>2270223</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>6055667</v>
+        <v>5311675</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>5013108</v>
+        <v>6012083</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>5500540</v>
+        <v>1461548</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>1639690</v>
+        <v>7929367</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>1914484</v>
+        <v>963093</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>3055762</v>
+        <v>9098159</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9456059</v>
+        <v>5114912</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>8935451</v>
+        <v>3861214</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>9616529</v>
+        <v>8119166</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>6189738</v>
+        <v>1170980</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>4989468</v>
+        <v>9831594</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>7967647</v>
+        <v>2431279</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>3671913</v>
+        <v>5712577</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>9336079</v>
+        <v>1839387</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>2315941</v>
+        <v>6900471</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>4929838</v>
+        <v>2017955</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>2431783</v>
+        <v>7831763</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>1721467</v>
+        <v>7805662</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>927715</v>
+        <v>7548539</v>
       </c>
     </row>
     <row r="13">
@@ -5104,100 +5104,100 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>6640459</v>
+        <v>980796</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5796868</v>
+        <v>3318402</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2307355</v>
+        <v>9589321</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>524557</v>
+        <v>6959941</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4279511</v>
+        <v>8576228</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>6040084</v>
+        <v>8675628</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>5654066</v>
+        <v>8048586</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2832796</v>
+        <v>8954630</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>68639</v>
+        <v>206729</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>3577245</v>
+        <v>2717116</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4999568</v>
+        <v>7908753</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>5530982</v>
+        <v>593534</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>6071579</v>
+        <v>9817380</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8917508</v>
+        <v>3107718</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>3739674</v>
+        <v>3547127</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>1926785</v>
+        <v>3141017</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>6536263</v>
+        <v>616629</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>3661734</v>
+        <v>3917235</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>1707108</v>
+        <v>146476</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>7005775</v>
+        <v>3073075</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>1905163</v>
+        <v>5963161</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>5621972</v>
+        <v>9280857</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>5933134</v>
+        <v>8568052</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>3354312</v>
+        <v>1745123</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>6199604</v>
+        <v>7089906</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>42508</v>
+        <v>7193224</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>2807647</v>
+        <v>4498667</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>1933462</v>
+        <v>9939970</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>2873521</v>
+        <v>520719</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>7988572</v>
+        <v>505353</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>4111122</v>
+        <v>9712180</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>5311575</v>
+        <v>7232153</v>
       </c>
     </row>
     <row r="14">
@@ -5207,100 +5207,100 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9727078</v>
+        <v>2040344</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6150217</v>
+        <v>9750610</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1049810</v>
+        <v>6393725</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>9328229</v>
+        <v>1876458</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>9479430</v>
+        <v>9022525</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>6290015</v>
+        <v>4841582</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>9305261</v>
+        <v>286475</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>8300321</v>
+        <v>7129865</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>3472192</v>
+        <v>4780462</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4346157</v>
+        <v>6542492</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>496985</v>
+        <v>9498768</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>4249726</v>
+        <v>7001147</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>3111270</v>
+        <v>1177976</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>3315433</v>
+        <v>7200873</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>5868940</v>
+        <v>4984788</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>6399697</v>
+        <v>547562</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>7001763</v>
+        <v>5592111</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>5640432</v>
+        <v>4235443</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>7856885</v>
+        <v>1380948</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>2211428</v>
+        <v>2426404</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>4780735</v>
+        <v>9329455</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>7979886</v>
+        <v>9854499</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>5522960</v>
+        <v>8639681</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>701268</v>
+        <v>3179270</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>6151562</v>
+        <v>8741952</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>5251761</v>
+        <v>9366555</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>4245169</v>
+        <v>2226400</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>9733267</v>
+        <v>7321981</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>5654050</v>
+        <v>4595224</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>4265692</v>
+        <v>437859</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>9751405</v>
+        <v>1063889</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>9111486</v>
+        <v>5786679</v>
       </c>
     </row>
     <row r="15">
@@ -5310,100 +5310,100 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7933639</v>
+        <v>4774652</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>404559</v>
+        <v>5010668</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>9417255</v>
+        <v>9550888</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>730116</v>
+        <v>7098405</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7561874</v>
+        <v>3545134</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2779795</v>
+        <v>7327545</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>5888619</v>
+        <v>8707458</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4950369</v>
+        <v>4355237</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>7548364</v>
+        <v>9084309</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>6144787</v>
+        <v>9699309</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>2059950</v>
+        <v>9334065</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>9845665</v>
+        <v>6526914</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>4146852</v>
+        <v>1406366</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>438788</v>
+        <v>5886914</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8525046</v>
+        <v>3541653</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2834588</v>
+        <v>1862893</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>8062967</v>
+        <v>497346</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>5589907</v>
+        <v>4170573</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>9647716</v>
+        <v>7443631</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>3252394</v>
+        <v>2126329</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>5494177</v>
+        <v>8869422</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>1146522</v>
+        <v>3081942</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>5909352</v>
+        <v>4224103</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>6413498</v>
+        <v>8253964</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3508333</v>
+        <v>4608444</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>1945296</v>
+        <v>736612</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>5713563</v>
+        <v>976529</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>4267385</v>
+        <v>7561038</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>5806367</v>
+        <v>1400458</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>6584674</v>
+        <v>5422240</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>3767357</v>
+        <v>462074</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>9608543</v>
+        <v>5733990</v>
       </c>
     </row>
     <row r="16">
@@ -5413,100 +5413,100 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>57326</v>
+        <v>9467629</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9622942</v>
+        <v>8920539</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4284663</v>
+        <v>2290592</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>128907</v>
+        <v>6558198</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5181358</v>
+        <v>3387254</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1746546</v>
+        <v>963269</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8136735</v>
+        <v>9796366</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>6822260</v>
+        <v>501826</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>8224604</v>
+        <v>7589320</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>9378568</v>
+        <v>6072613</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1367564</v>
+        <v>1427448</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>9851112</v>
+        <v>2074676</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4636658</v>
+        <v>4565163</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>7974647</v>
+        <v>9740383</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4823956</v>
+        <v>4835438</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1881268</v>
+        <v>9946752</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>4583193</v>
+        <v>1330476</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>938272</v>
+        <v>9386702</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1299742</v>
+        <v>3356373</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>2315201</v>
+        <v>7107112</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>6428237</v>
+        <v>2123352</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>4797754</v>
+        <v>2277043</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>7743713</v>
+        <v>1811639</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>9713481</v>
+        <v>9926545</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>3688295</v>
+        <v>656094</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>2250618</v>
+        <v>8295328</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>8051162</v>
+        <v>5811542</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>7152634</v>
+        <v>4536224</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>4979730</v>
+        <v>5080638</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>7698724</v>
+        <v>1036607</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>760855</v>
+        <v>3375913</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>4054346</v>
+        <v>8539368</v>
       </c>
     </row>
     <row r="17">
@@ -5516,100 +5516,100 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>899885</v>
+        <v>2886089</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2742773</v>
+        <v>4127791</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>548124</v>
+        <v>3724224</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4916432</v>
+        <v>315999</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4347010</v>
+        <v>8514627</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3169917</v>
+        <v>3447078</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5478136</v>
+        <v>6115982</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>333707</v>
+        <v>9020002</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>9657704</v>
+        <v>947967</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1907451</v>
+        <v>2707668</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>8309669</v>
+        <v>4917392</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>7581671</v>
+        <v>5564896</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>6648427</v>
+        <v>6549764</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8170799</v>
+        <v>4623615</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1544975</v>
+        <v>8328659</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>3411074</v>
+        <v>7321824</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>2786026</v>
+        <v>6470666</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>865136</v>
+        <v>4984579</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>2462188</v>
+        <v>4279539</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>1509636</v>
+        <v>6582865</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>2544590</v>
+        <v>2132726</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>1819081</v>
+        <v>5352963</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>1243636</v>
+        <v>1161991</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>122627</v>
+        <v>9765896</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>3961511</v>
+        <v>6381569</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>45996</v>
+        <v>4639987</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>813682</v>
+        <v>2215107</v>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>7427680</v>
+        <v>6913985</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>5269457</v>
+        <v>3995138</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>8755635</v>
+        <v>4031145</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>351574</v>
+        <v>3829131</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>1678631</v>
+        <v>3560437</v>
       </c>
     </row>
     <row r="18">
@@ -5619,100 +5619,100 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>349956</v>
+        <v>7340975</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7966022</v>
+        <v>6839718</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1012942</v>
+        <v>4113357</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>4305773</v>
+        <v>4231557</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9089264</v>
+        <v>9855079</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>5059452</v>
+        <v>5560885</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1791640</v>
+        <v>4766611</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>271101</v>
+        <v>9259241</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>127034</v>
+        <v>3645809</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>9300647</v>
+        <v>6981564</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>9548437</v>
+        <v>5354180</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>7663226</v>
+        <v>8574546</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>6694924</v>
+        <v>8036628</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>5856497</v>
+        <v>7587349</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>7649596</v>
+        <v>7840090</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>3098865</v>
+        <v>5795832</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>7310360</v>
+        <v>4606652</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>5271388</v>
+        <v>8138429</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>5219739</v>
+        <v>3448946</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>4918309</v>
+        <v>6451859</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>7936982</v>
+        <v>1530365</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>2286682</v>
+        <v>2416589</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>4792829</v>
+        <v>7322888</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>3592461</v>
+        <v>8733856</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>996123</v>
+        <v>7918214</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>1076128</v>
+        <v>3255029</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>83315</v>
+        <v>6317427</v>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>8633416</v>
+        <v>6879300</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>8377167</v>
+        <v>2175159</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>3527904</v>
+        <v>4512272</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>2296052</v>
+        <v>709734</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>7226453</v>
+        <v>2463409</v>
       </c>
     </row>
     <row r="19">
@@ -5722,100 +5722,100 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5845327</v>
+        <v>6552032</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>133162</v>
+        <v>1175014</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>7400911</v>
+        <v>5052867</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8980911</v>
+        <v>8299051</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3059767</v>
+        <v>7936810</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2001153</v>
+        <v>8285765</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3795316</v>
+        <v>4395784</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>3080579</v>
+        <v>6393981</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>9406276</v>
+        <v>357272</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>3037103</v>
+        <v>9049475</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3375981</v>
+        <v>4183651</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>9818956</v>
+        <v>9663414</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>3956351</v>
+        <v>4734299</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1297374</v>
+        <v>7242054</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>7785995</v>
+        <v>4540587</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>5149919</v>
+        <v>8129663</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>4376251</v>
+        <v>8704487</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>7263094</v>
+        <v>2028107</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>2624042</v>
+        <v>8579281</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>5221108</v>
+        <v>224290</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>6534866</v>
+        <v>5781341</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>5186526</v>
+        <v>690726</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>2840826</v>
+        <v>2026476</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>5692956</v>
+        <v>6572651</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3096993</v>
+        <v>404626</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>1624846</v>
+        <v>8072490</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>6949516</v>
+        <v>2746581</v>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>8829439</v>
+        <v>7628992</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>9861405</v>
+        <v>7351604</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>1678784</v>
+        <v>7613601</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>6049430</v>
+        <v>2081005</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>7214385</v>
+        <v>6360864</v>
       </c>
     </row>
     <row r="20">
@@ -5825,100 +5825,100 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>4555099</v>
+        <v>333420</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5046001</v>
+        <v>1165963</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8375469</v>
+        <v>9743114</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8147700</v>
+        <v>5586424</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>379521</v>
+        <v>1279172</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5517419</v>
+        <v>5490040</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4480139</v>
+        <v>6849469</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2062713</v>
+        <v>6784291</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>6942496</v>
+        <v>2175878</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>992525</v>
+        <v>423290</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2716087</v>
+        <v>4004468</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>6360845</v>
+        <v>8580663</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>3446207</v>
+        <v>1526062</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>3189325</v>
+        <v>4318406</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1602432</v>
+        <v>7058348</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>8948411</v>
+        <v>4578681</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>163220</v>
+        <v>2247649</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>4445197</v>
+        <v>3181419</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>9528681</v>
+        <v>4320874</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>3499312</v>
+        <v>2926829</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>735897</v>
+        <v>5385171</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>6085513</v>
+        <v>8195004</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>8983996</v>
+        <v>1196016</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>7525814</v>
+        <v>7222650</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>1565893</v>
+        <v>9430101</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>4743029</v>
+        <v>3574364</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>4027649</v>
+        <v>1705314</v>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>3229843</v>
+        <v>3885924</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>4656024</v>
+        <v>2104686</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>1773571</v>
+        <v>1253357</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>328916</v>
+        <v>2009533</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>7172679</v>
+        <v>9672707</v>
       </c>
     </row>
     <row r="21">
@@ -5928,100 +5928,100 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3812052</v>
+        <v>4808831</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6904280</v>
+        <v>7353329</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1157372</v>
+        <v>633072</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>9154040</v>
+        <v>1589579</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1108432</v>
+        <v>8639269</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7180415</v>
+        <v>2583834</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1259648</v>
+        <v>472088</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>6475934</v>
+        <v>1938670</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1993003</v>
+        <v>4811524</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3209214</v>
+        <v>389864</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>8432722</v>
+        <v>5383723</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>4167305</v>
+        <v>7920158</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>7420883</v>
+        <v>8358342</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>5131572</v>
+        <v>6580112</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6885336</v>
+        <v>3476594</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>3343910</v>
+        <v>7060579</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>8366078</v>
+        <v>7033311</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1742634</v>
+        <v>3351998</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>9727087</v>
+        <v>7603921</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1019672</v>
+        <v>7532329</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>9407577</v>
+        <v>2101080</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>9651392</v>
+        <v>6324657</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>5988943</v>
+        <v>8468910</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>9611627</v>
+        <v>1663110</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3592910</v>
+        <v>6059011</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>4908972</v>
+        <v>3837057</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>1952817</v>
+        <v>2764200</v>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>8739185</v>
+        <v>4834912</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>3128336</v>
+        <v>4346334</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>7547489</v>
+        <v>6737071</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>4105259</v>
+        <v>6870468</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>1648026</v>
+        <v>143061</v>
       </c>
     </row>
     <row r="22">
@@ -6031,100 +6031,100 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7185302</v>
+        <v>3608413</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9057456</v>
+        <v>6846572</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>9878804</v>
+        <v>2494508</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>8665349</v>
+        <v>8967502</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5194893</v>
+        <v>3071554</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9125682</v>
+        <v>8839491</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8206633</v>
+        <v>5558744</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>7490755</v>
+        <v>5779904</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2963206</v>
+        <v>7171833</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2092311</v>
+        <v>7916007</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>117238</v>
+        <v>774270</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>735188</v>
+        <v>5910867</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>5426190</v>
+        <v>5815324</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>6110339</v>
+        <v>5479033</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>7193557</v>
+        <v>4465138</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>325488</v>
+        <v>4221659</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>1811816</v>
+        <v>7480654</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1797268</v>
+        <v>7393342</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8854428</v>
+        <v>5301725</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>8761205</v>
+        <v>7041494</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>4973737</v>
+        <v>5517637</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>1275924</v>
+        <v>9891127</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2725988</v>
+        <v>2508562</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>2145854</v>
+        <v>6405982</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>6439727</v>
+        <v>9734890</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>957530</v>
+        <v>3828177</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>4213120</v>
+        <v>8148397</v>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>3299725</v>
+        <v>6783850</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>805808</v>
+        <v>2880024</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>2044019</v>
+        <v>4085074</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>4218256</v>
+        <v>2316486</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>8962824</v>
+        <v>7358346</v>
       </c>
     </row>
     <row r="23">
@@ -6134,100 +6134,100 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>851852</v>
+        <v>3148208</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1370399</v>
+        <v>5130716</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3105722</v>
+        <v>6543778</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5644420</v>
+        <v>8331493</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9892189</v>
+        <v>374431</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3698938</v>
+        <v>3926048</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1763434</v>
+        <v>3356889</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4667997</v>
+        <v>8972956</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>6673630</v>
+        <v>1854143</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5709717</v>
+        <v>5184814</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7437162</v>
+        <v>2592137</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>7551649</v>
+        <v>2457522</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3757443</v>
+        <v>6090433</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>7999412</v>
+        <v>8153782</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3918688</v>
+        <v>209317</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>7451806</v>
+        <v>8565287</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>5973703</v>
+        <v>786775</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1605473</v>
+        <v>1390686</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>5567812</v>
+        <v>1161355</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>5227447</v>
+        <v>859142</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>8058323</v>
+        <v>4770013</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>7148515</v>
+        <v>5276526</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>4024628</v>
+        <v>7673624</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>5260980</v>
+        <v>5095622</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>3960627</v>
+        <v>4369047</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>5002046</v>
+        <v>71308</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>9043745</v>
+        <v>207964</v>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>2048573</v>
+        <v>8637196</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>448668</v>
+        <v>8409303</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>2254206</v>
+        <v>8953851</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>7378054</v>
+        <v>5725731</v>
       </c>
       <c r="AG23" s="3" t="n">
-        <v>432660</v>
+        <v>2417674</v>
       </c>
     </row>
     <row r="24">
@@ -6237,100 +6237,100 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>6179919</v>
+        <v>1515974</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>9061940</v>
+        <v>800564</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2121537</v>
+        <v>4227027</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>7616642</v>
+        <v>3467742</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>7096025</v>
+        <v>9244629</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2956936</v>
+        <v>6416486</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>1085210</v>
+        <v>3007781</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2264622</v>
+        <v>8029582</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>9820004</v>
+        <v>2503989</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>3239955</v>
+        <v>295922</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>2878477</v>
+        <v>1572913</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>8851026</v>
+        <v>8600096</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>8902680</v>
+        <v>2891044</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5764986</v>
+        <v>990593</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1934947</v>
+        <v>6363841</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>8897461</v>
+        <v>4442428</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>1686691</v>
+        <v>2449483</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>9650572</v>
+        <v>3046305</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>8426257</v>
+        <v>3426292</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>4735063</v>
+        <v>1780659</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>2346980</v>
+        <v>4858617</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>3568706</v>
+        <v>3398460</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>2625219</v>
+        <v>5180351</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2951969</v>
+        <v>7859393</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>648046</v>
+        <v>966393</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>7456611</v>
+        <v>5214872</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>6469362</v>
+        <v>4359278</v>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>6802899</v>
+        <v>7370362</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>7829921</v>
+        <v>6884892</v>
       </c>
       <c r="AE24" s="3" t="n">
-        <v>3211242</v>
+        <v>4981386</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>1889358</v>
+        <v>8878401</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>5856280</v>
+        <v>6035508</v>
       </c>
     </row>
     <row r="25">
@@ -6340,100 +6340,100 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>4290614</v>
+        <v>9527626</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>7792157</v>
+        <v>5830240</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>8130123</v>
+        <v>7553475</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5344895</v>
+        <v>8351247</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7328434</v>
+        <v>3597680</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9504615</v>
+        <v>8532302</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1368118</v>
+        <v>289481</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>5859080</v>
+        <v>2046784</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>5363080</v>
+        <v>7245482</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8381363</v>
+        <v>574757</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>9234949</v>
+        <v>2399060</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9803339</v>
+        <v>6698027</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1498184</v>
+        <v>1243504</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>3994841</v>
+        <v>6461677</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>3648286</v>
+        <v>507364</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>1383192</v>
+        <v>9913503</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>1491639</v>
+        <v>6480650</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>8248468</v>
+        <v>2910696</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>4362982</v>
+        <v>1323708</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>3465131</v>
+        <v>1613523</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>9340592</v>
+        <v>512942</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>5152316</v>
+        <v>4399885</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>1483335</v>
+        <v>4386803</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>2903558</v>
+        <v>1873914</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>8525441</v>
+        <v>2774213</v>
       </c>
       <c r="AA25" s="3" t="n">
-        <v>6714721</v>
+        <v>8792747</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>5795088</v>
+        <v>3894527</v>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>2527427</v>
+        <v>345711</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>7707212</v>
+        <v>9074941</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>8071900</v>
+        <v>6132329</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>885547</v>
+        <v>1965509</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>7233970</v>
+        <v>6316426</v>
       </c>
     </row>
     <row r="26">
@@ -6443,100 +6443,100 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>4244454</v>
+        <v>8815104</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>7585515</v>
+        <v>7957973</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>6051792</v>
+        <v>3858222</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7290739</v>
+        <v>1926267</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>8266236</v>
+        <v>4134014</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3717477</v>
+        <v>8784177</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3953205</v>
+        <v>3197734</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>9085248</v>
+        <v>7733728</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>170627</v>
+        <v>2704703</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>8625624</v>
+        <v>2544534</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>2682029</v>
+        <v>4070968</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>5120722</v>
+        <v>8044812</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>4476876</v>
+        <v>1953380</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>6001949</v>
+        <v>7496858</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>959354</v>
+        <v>862103</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>1859310</v>
+        <v>5765522</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>7617808</v>
+        <v>8517417</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>416019</v>
+        <v>340324</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>903662</v>
+        <v>4645348</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6874667</v>
+        <v>8238890</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>430552</v>
+        <v>9937531</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>5707683</v>
+        <v>1565527</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>4222216</v>
+        <v>8058165</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2419762</v>
+        <v>1700062</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>7661825</v>
+        <v>9897110</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>9875452</v>
+        <v>7664374</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>2599891</v>
+        <v>4365454</v>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>8974235</v>
+        <v>3489048</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>6624767</v>
+        <v>5703558</v>
       </c>
       <c r="AE26" s="3" t="n">
-        <v>7832721</v>
+        <v>9549113</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>7540417</v>
+        <v>8392603</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>6599181</v>
+        <v>719103</v>
       </c>
     </row>
     <row r="27">
@@ -6546,100 +6546,100 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2658256</v>
+        <v>3362699</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>84172</v>
+        <v>8994178</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4671138</v>
+        <v>7785379</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1956109</v>
+        <v>4745090</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4863824</v>
+        <v>3955373</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8832166</v>
+        <v>1720991</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3923517</v>
+        <v>2309508</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>6734849</v>
+        <v>1951107</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6095899</v>
+        <v>7736287</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2371229</v>
+        <v>214908</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4311518</v>
+        <v>9407580</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>6470268</v>
+        <v>6758456</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>8643747</v>
+        <v>2659021</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>359561</v>
+        <v>4378462</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3628674</v>
+        <v>9740490</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>8264047</v>
+        <v>2132973</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1305829</v>
+        <v>1869697</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1956466</v>
+        <v>8867579</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>210651</v>
+        <v>90748</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6872452</v>
+        <v>9146859</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>8335599</v>
+        <v>5685037</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>9343240</v>
+        <v>8914351</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9186374</v>
+        <v>1232727</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>5948088</v>
+        <v>6787903</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>3308148</v>
+        <v>6850864</v>
       </c>
       <c r="AA27" s="3" t="n">
-        <v>4131160</v>
+        <v>1559278</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>9687426</v>
+        <v>2918379</v>
       </c>
       <c r="AC27" s="3" t="n">
-        <v>7755746</v>
+        <v>2327953</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>1192440</v>
+        <v>4364600</v>
       </c>
       <c r="AE27" s="3" t="n">
-        <v>179302</v>
+        <v>9260099</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>7714786</v>
+        <v>9555483</v>
       </c>
       <c r="AG27" s="3" t="n">
-        <v>8823573</v>
+        <v>5858472</v>
       </c>
     </row>
     <row r="28">
@@ -6649,100 +6649,100 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>6393379</v>
+        <v>4107419</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1402027</v>
+        <v>4300080</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>6340711</v>
+        <v>1800982</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>247530</v>
+        <v>4489108</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>9190016</v>
+        <v>5025149</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>5211599</v>
+        <v>4967207</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2831792</v>
+        <v>4564981</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1039854</v>
+        <v>562456</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>9991674</v>
+        <v>4047154</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>758881</v>
+        <v>8416884</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>9477166</v>
+        <v>3938305</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1380908</v>
+        <v>6525798</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>5750730</v>
+        <v>307962</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>2699426</v>
+        <v>1478175</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>5508001</v>
+        <v>6627841</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>2891011</v>
+        <v>6731335</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>6017127</v>
+        <v>4835210</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>5758611</v>
+        <v>7802777</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>1269443</v>
+        <v>7098365</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>6540619</v>
+        <v>9659281</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>5030980</v>
+        <v>7872313</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>1283302</v>
+        <v>3998243</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>9689748</v>
+        <v>7086678</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>950878</v>
+        <v>7560674</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5125168</v>
+        <v>1614723</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>351940</v>
+        <v>8913043</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>3610873</v>
+        <v>7365126</v>
       </c>
       <c r="AC28" s="3" t="n">
-        <v>6854733</v>
+        <v>5628497</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>7200723</v>
+        <v>8614000</v>
       </c>
       <c r="AE28" s="3" t="n">
-        <v>8582884</v>
+        <v>5036405</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>135002</v>
+        <v>1291208</v>
       </c>
       <c r="AG28" s="3" t="n">
-        <v>9721809</v>
+        <v>4062695</v>
       </c>
     </row>
     <row r="29">
@@ -6752,100 +6752,100 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>641680</v>
+        <v>3316844</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7049596</v>
+        <v>3516499</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6070141</v>
+        <v>3033676</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>8172145</v>
+        <v>8772474</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6574699</v>
+        <v>2276932</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9993923</v>
+        <v>702068</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3828558</v>
+        <v>7704672</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4176281</v>
+        <v>4275670</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2029154</v>
+        <v>7904073</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4897040</v>
+        <v>3319530</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4645265</v>
+        <v>9927999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>8422014</v>
+        <v>5973423</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>3917501</v>
+        <v>9930246</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1572347</v>
+        <v>7073502</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5738562</v>
+        <v>2817793</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>6469065</v>
+        <v>9274754</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>5758007</v>
+        <v>5099813</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>6952968</v>
+        <v>2501720</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>2239122</v>
+        <v>5644900</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>1663957</v>
+        <v>8254807</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>8622490</v>
+        <v>9158319</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>2008916</v>
+        <v>7978410</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>5527181</v>
+        <v>3828107</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2702779</v>
+        <v>607382</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>8002393</v>
+        <v>7765105</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>8283360</v>
+        <v>3965026</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>4550693</v>
+        <v>961310</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>5973246</v>
+        <v>1297623</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>4506168</v>
+        <v>3573924</v>
       </c>
       <c r="AE29" s="3" t="n">
-        <v>9239870</v>
+        <v>4664887</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>3876922</v>
+        <v>8064089</v>
       </c>
       <c r="AG29" s="3" t="n">
-        <v>1107849</v>
+        <v>1715572</v>
       </c>
     </row>
     <row r="30">
@@ -6855,100 +6855,100 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1164788</v>
+        <v>1517833</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4615035</v>
+        <v>924645</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>840173</v>
+        <v>7319707</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5692450</v>
+        <v>4799039</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>9543624</v>
+        <v>1674828</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6444335</v>
+        <v>2174898</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1656390</v>
+        <v>625858</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>83095</v>
+        <v>7361116</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2242083</v>
+        <v>608588</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5050488</v>
+        <v>9021657</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>7787351</v>
+        <v>595300</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>820761</v>
+        <v>3919272</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1495634</v>
+        <v>1460998</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2905907</v>
+        <v>9205970</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4462257</v>
+        <v>3011776</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>4698693</v>
+        <v>705841</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>7414607</v>
+        <v>2762623</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>723963</v>
+        <v>8100065</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1458402</v>
+        <v>7790665</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>2577675</v>
+        <v>1421083</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>8499547</v>
+        <v>2658476</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>6721251</v>
+        <v>2891748</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1089034</v>
+        <v>2916578</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>3879294</v>
+        <v>7219567</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2753722</v>
+        <v>6661087</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>2662786</v>
+        <v>9753716</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>6117358</v>
+        <v>5133397</v>
       </c>
       <c r="AC30" s="3" t="n">
-        <v>6380785</v>
+        <v>8386336</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>9424832</v>
+        <v>8813712</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>3433045</v>
+        <v>6811194</v>
       </c>
       <c r="AF30" s="3" t="n">
-        <v>1410167</v>
+        <v>2945080</v>
       </c>
       <c r="AG30" s="3" t="n">
-        <v>8211497</v>
+        <v>6742603</v>
       </c>
     </row>
     <row r="31">
@@ -6958,100 +6958,100 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3273440</v>
+        <v>1571419</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>4413343</v>
+        <v>924236</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>298423</v>
+        <v>4494875</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6193970</v>
+        <v>6835461</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>8654122</v>
+        <v>5010623</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5504685</v>
+        <v>8693022</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2275141</v>
+        <v>2344195</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>329086</v>
+        <v>5302598</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1231589</v>
+        <v>2105641</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>3291616</v>
+        <v>921269</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>5110176</v>
+        <v>4346377</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>8635025</v>
+        <v>8333195</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>6824191</v>
+        <v>3718393</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>4887055</v>
+        <v>4848461</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>3330530</v>
+        <v>2279199</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>1350468</v>
+        <v>3491739</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>1582219</v>
+        <v>2620912</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>7027383</v>
+        <v>8446997</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>3127762</v>
+        <v>6209482</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18146</v>
+        <v>4102391</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>1575555</v>
+        <v>582018</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>7339208</v>
+        <v>6233637</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>4824313</v>
+        <v>5142064</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>7424559</v>
+        <v>6853839</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>9955229</v>
+        <v>8595616</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>2848051</v>
+        <v>5117584</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>7903429</v>
+        <v>6743706</v>
       </c>
       <c r="AC31" s="3" t="n">
-        <v>5806997</v>
+        <v>1857602</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>6586417</v>
+        <v>6357996</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>8003199</v>
+        <v>6466293</v>
       </c>
       <c r="AF31" s="3" t="n">
-        <v>8384382</v>
+        <v>2937467</v>
       </c>
       <c r="AG31" s="3" t="n">
-        <v>1969799</v>
+        <v>300669</v>
       </c>
     </row>
     <row r="32">
@@ -7061,100 +7061,100 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>4239409</v>
+        <v>750493</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>9868515</v>
+        <v>6034701</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>2108628</v>
+        <v>2343119</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2432383</v>
+        <v>9526483</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>889170</v>
+        <v>8700582</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8033831</v>
+        <v>293551</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>7230400</v>
+        <v>4125993</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>7675453</v>
+        <v>8879802</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>8251602</v>
+        <v>3971593</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>4298837</v>
+        <v>4490636</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>8041856</v>
+        <v>1774894</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>6540815</v>
+        <v>4370336</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1014271</v>
+        <v>9358136</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>559543</v>
+        <v>5215304</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2939528</v>
+        <v>8204497</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>5595072</v>
+        <v>2025023</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>4707940</v>
+        <v>9051420</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>5399712</v>
+        <v>8042134</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>6369370</v>
+        <v>5338317</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>6770692</v>
+        <v>7101205</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>8354167</v>
+        <v>1596308</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>3320593</v>
+        <v>1315186</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>7461395</v>
+        <v>227332</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>1035171</v>
+        <v>3081297</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8679240</v>
+        <v>8388527</v>
       </c>
       <c r="AA32" s="3" t="n">
-        <v>4916916</v>
+        <v>9888813</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>1080340</v>
+        <v>2705595</v>
       </c>
       <c r="AC32" s="3" t="n">
-        <v>9655196</v>
+        <v>1920542</v>
       </c>
       <c r="AD32" s="3" t="n">
-        <v>8046417</v>
+        <v>494929</v>
       </c>
       <c r="AE32" s="3" t="n">
-        <v>9286200</v>
+        <v>6360803</v>
       </c>
       <c r="AF32" s="3" t="n">
-        <v>1034587</v>
+        <v>8971570</v>
       </c>
       <c r="AG32" s="3" t="n">
-        <v>3798822</v>
+        <v>6847204</v>
       </c>
     </row>
     <row r="33">
@@ -7164,100 +7164,100 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4829278</v>
+        <v>6926371</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>5089816</v>
+        <v>338948</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>7373468</v>
+        <v>9927786</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>5504016</v>
+        <v>9616968</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>800210</v>
+        <v>4267933</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8361931</v>
+        <v>5474161</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7224717</v>
+        <v>5418225</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>6466757</v>
+        <v>2810451</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>4290047</v>
+        <v>2464010</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>8126015</v>
+        <v>3885579</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>4957969</v>
+        <v>5080348</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>1631653</v>
+        <v>4613095</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>3999520</v>
+        <v>7839313</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>7244130</v>
+        <v>5716763</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>6626449</v>
+        <v>8562855</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>5509741</v>
+        <v>5909184</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>7269262</v>
+        <v>50359</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>5671606</v>
+        <v>9233352</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9842539</v>
+        <v>444056</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>8652567</v>
+        <v>2864522</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>2522047</v>
+        <v>8614370</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>459429</v>
+        <v>3957876</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>8913590</v>
+        <v>3109981</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>5912635</v>
+        <v>636114</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>8332054</v>
+        <v>9669430</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>768620</v>
+        <v>83812</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>3663341</v>
+        <v>6025287</v>
       </c>
       <c r="AC33" s="3" t="n">
-        <v>2082057</v>
+        <v>1381392</v>
       </c>
       <c r="AD33" s="3" t="n">
-        <v>295104</v>
+        <v>8345223</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>5441487</v>
+        <v>8247575</v>
       </c>
       <c r="AF33" s="3" t="n">
-        <v>7353963</v>
+        <v>6161833</v>
       </c>
       <c r="AG33" s="3" t="n">
-        <v>9679833</v>
+        <v>320212</v>
       </c>
     </row>
     <row r="34">
@@ -7267,100 +7267,100 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>8657888</v>
+        <v>3145400</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>8273799</v>
+        <v>2059595</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>8324424</v>
+        <v>4779804</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>7917196</v>
+        <v>6256110</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>394986</v>
+        <v>1844435</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3583666</v>
+        <v>7723493</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>7089987</v>
+        <v>6759956</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>6410561</v>
+        <v>3114465</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9981008</v>
+        <v>4254771</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>9087212</v>
+        <v>7142696</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>6823719</v>
+        <v>3841794</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>3466714</v>
+        <v>7140419</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>3709202</v>
+        <v>7061890</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>2190061</v>
+        <v>726692</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>4110199</v>
+        <v>9362674</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>4450374</v>
+        <v>3872392</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>2333706</v>
+        <v>8855378</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>8936908</v>
+        <v>2047588</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>5556041</v>
+        <v>172633</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>3628999</v>
+        <v>1130526</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>9773674</v>
+        <v>2743541</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>3888582</v>
+        <v>9255691</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>4314878</v>
+        <v>1132969</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>7755581</v>
+        <v>6954851</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>5529315</v>
+        <v>4144486</v>
       </c>
       <c r="AA34" s="3" t="n">
-        <v>5679627</v>
+        <v>122342</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>5098642</v>
+        <v>7000629</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>191158</v>
+        <v>3581156</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>9839575</v>
+        <v>8233220</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>9413620</v>
+        <v>6269220</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>2824434</v>
+        <v>1974628</v>
       </c>
       <c r="AG34" s="3" t="n">
-        <v>421457</v>
+        <v>3700354</v>
       </c>
     </row>
     <row r="35">
@@ -7370,100 +7370,100 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>5760445</v>
+        <v>7239395</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>758886</v>
+        <v>228725</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6121652</v>
+        <v>5695441</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2278078</v>
+        <v>8379472</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>9733258</v>
+        <v>1047313</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>982916</v>
+        <v>6655681</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>7306449</v>
+        <v>1838020</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3177929</v>
+        <v>9782118</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3845186</v>
+        <v>5000348</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>9171912</v>
+        <v>3798513</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>8720747</v>
+        <v>1776534</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>3168536</v>
+        <v>7438110</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>481985</v>
+        <v>6916075</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>792629</v>
+        <v>2031714</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1282211</v>
+        <v>2962507</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>9327825</v>
+        <v>2062102</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>2445499</v>
+        <v>9268842</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>6783144</v>
+        <v>4884727</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>8025920</v>
+        <v>570581</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>9367778</v>
+        <v>5661727</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>9275095</v>
+        <v>6398727</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>8948362</v>
+        <v>9150731</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>624441</v>
+        <v>4727146</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>9715658</v>
+        <v>8873694</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>7570163</v>
+        <v>2040661</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>9773070</v>
+        <v>8689972</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>9644138</v>
+        <v>8385717</v>
       </c>
       <c r="AC35" s="3" t="n">
-        <v>6821302</v>
+        <v>3385624</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>3108796</v>
+        <v>9887792</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>4085704</v>
+        <v>3812245</v>
       </c>
       <c r="AF35" s="3" t="n">
-        <v>6753282</v>
+        <v>8018075</v>
       </c>
       <c r="AG35" s="3" t="n">
-        <v>1439229</v>
+        <v>2481822</v>
       </c>
     </row>
   </sheetData>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-25 10:57:55</t>
+          <t>2026-04-25 11:29:47</t>
         </is>
       </c>
     </row>

--- a/Proyecto_Python/src/main/resources/matrices/matrix_Caso2_32x32.xlsx
+++ b/Proyecto_Python/src/main/resources/matrices/matrix_Caso2_32x32.xlsx
@@ -660,100 +660,100 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4881073</v>
+        <v>8755914</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2378575</v>
+        <v>6719290</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5672972</v>
+        <v>7529553</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>8169779</v>
+        <v>1442712</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>8151562</v>
+        <v>4214043</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4897090</v>
+        <v>8099829</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7419920</v>
+        <v>5665456</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>8089623</v>
+        <v>2243886</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4503299</v>
+        <v>813254</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>2322410</v>
+        <v>8414564</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5178655</v>
+        <v>9787900</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>23570</v>
+        <v>9798166</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>7533819</v>
+        <v>4743202</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>6424108</v>
+        <v>3621464</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>3281737</v>
+        <v>985013</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>7422693</v>
+        <v>9196420</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>8303674</v>
+        <v>5952095</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>8624695</v>
+        <v>9348555</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>3255331</v>
+        <v>8630116</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1904912</v>
+        <v>3842797</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>8607166</v>
+        <v>7980738</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>4742521</v>
+        <v>6949354</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>8044940</v>
+        <v>5364268</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>6727669</v>
+        <v>5723372</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9700246</v>
+        <v>9918960</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>2065600</v>
+        <v>8512302</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>5242561</v>
+        <v>7144378</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>3383889</v>
+        <v>1683714</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>8739444</v>
+        <v>5169114</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>5114480</v>
+        <v>3398172</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>308659</v>
+        <v>6732724</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>4590757</v>
+        <v>175908</v>
       </c>
     </row>
     <row r="5">
@@ -763,100 +763,100 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>238779</v>
+        <v>5065044</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7002324</v>
+        <v>9603781</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2075656</v>
+        <v>907264</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7047933</v>
+        <v>5179404</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8762051</v>
+        <v>5623866</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2253779</v>
+        <v>3030544</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8017516</v>
+        <v>9559935</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>9116638</v>
+        <v>8694711</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3226851</v>
+        <v>5897372</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4137449</v>
+        <v>111976</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>215473</v>
+        <v>224092</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1615964</v>
+        <v>4112581</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>933866</v>
+        <v>5472114</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>5518996</v>
+        <v>8604548</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>726906</v>
+        <v>4690017</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>7206863</v>
+        <v>6420520</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>7897630</v>
+        <v>9095874</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>4855141</v>
+        <v>1195075</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>7096648</v>
+        <v>2446937</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7209771</v>
+        <v>1310460</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>3647402</v>
+        <v>123834</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>9962644</v>
+        <v>7299981</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>9982139</v>
+        <v>4690724</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>2205806</v>
+        <v>411250</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8113278</v>
+        <v>7327735</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>4695027</v>
+        <v>7285944</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>2434656</v>
+        <v>9078767</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>692772</v>
+        <v>1863380</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>5495540</v>
+        <v>9194547</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>8152203</v>
+        <v>7315374</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>3314763</v>
+        <v>7293454</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>5742743</v>
+        <v>9133049</v>
       </c>
     </row>
     <row r="6">
@@ -866,100 +866,100 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1886074</v>
+        <v>7059456</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1391869</v>
+        <v>1358078</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7111563</v>
+        <v>162493</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6779419</v>
+        <v>8610861</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>9494502</v>
+        <v>1403121</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>8907260</v>
+        <v>9978615</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1885660</v>
+        <v>428190</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8623714</v>
+        <v>8149011</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1248694</v>
+        <v>813082</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4681319</v>
+        <v>6064001</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>8874839</v>
+        <v>7624054</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>3638491</v>
+        <v>8126739</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>4782223</v>
+        <v>2629441</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>7499929</v>
+        <v>4173035</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2392105</v>
+        <v>6825512</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>8763966</v>
+        <v>4000670</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>3857118</v>
+        <v>5357480</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2799864</v>
+        <v>4546571</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>5879917</v>
+        <v>4415988</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1615809</v>
+        <v>3115781</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>7155356</v>
+        <v>5282127</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>7889820</v>
+        <v>6908081</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>408036</v>
+        <v>3054276</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>5058863</v>
+        <v>4805199</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>4813063</v>
+        <v>3751181</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>4199691</v>
+        <v>3916207</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>7576543</v>
+        <v>909163</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>5245936</v>
+        <v>1288534</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>4507712</v>
+        <v>5768747</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>2551215</v>
+        <v>2814101</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>4031047</v>
+        <v>5470005</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>6909366</v>
+        <v>4476669</v>
       </c>
     </row>
     <row r="7">
@@ -969,100 +969,100 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7003187</v>
+        <v>128954</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3231504</v>
+        <v>2473682</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6683303</v>
+        <v>7028644</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>670793</v>
+        <v>2351850</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>757120</v>
+        <v>6337226</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1503631</v>
+        <v>1664331</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7542041</v>
+        <v>464152</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2226842</v>
+        <v>1344704</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>9919342</v>
+        <v>8343192</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>3449221</v>
+        <v>2823931</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6495597</v>
+        <v>7241498</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>6315062</v>
+        <v>4618934</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>860129</v>
+        <v>1632925</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4343395</v>
+        <v>589475</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1785590</v>
+        <v>487918</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>7285443</v>
+        <v>7330466</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>4086568</v>
+        <v>4971469</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2924677</v>
+        <v>5349031</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>988747</v>
+        <v>9483732</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>7643053</v>
+        <v>3980523</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>4993651</v>
+        <v>144536</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>8721552</v>
+        <v>8722778</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>7293825</v>
+        <v>6975473</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>9226307</v>
+        <v>6862278</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3179626</v>
+        <v>4124188</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>7045050</v>
+        <v>36642</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>889643</v>
+        <v>7565936</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>6515609</v>
+        <v>4632184</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>9538013</v>
+        <v>8841062</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1246287</v>
+        <v>1983288</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>4836776</v>
+        <v>4363560</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>1984837</v>
+        <v>274684</v>
       </c>
     </row>
     <row r="8">
@@ -1072,100 +1072,100 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9089941</v>
+        <v>1600553</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8143295</v>
+        <v>5560043</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5677861</v>
+        <v>7858931</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>364203</v>
+        <v>79318</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>8803898</v>
+        <v>240620</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4574265</v>
+        <v>1945242</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>9078136</v>
+        <v>3983064</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>7533438</v>
+        <v>2310725</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4720519</v>
+        <v>6451198</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2851844</v>
+        <v>4654160</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>8476266</v>
+        <v>2302184</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>5767272</v>
+        <v>1815219</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>5532227</v>
+        <v>8628019</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>1067539</v>
+        <v>1409199</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>469185</v>
+        <v>3343531</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1830709</v>
+        <v>7550773</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>6206004</v>
+        <v>9149801</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>4367701</v>
+        <v>4640926</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>6531711</v>
+        <v>7521748</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>4841508</v>
+        <v>5868428</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>6066861</v>
+        <v>8900037</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>4786165</v>
+        <v>1135322</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>143940</v>
+        <v>6219908</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>195445</v>
+        <v>4032939</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>3942361</v>
+        <v>5293577</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>3385366</v>
+        <v>6232557</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>7856125</v>
+        <v>1804840</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>2779678</v>
+        <v>8122577</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>4633385</v>
+        <v>8019787</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>8631483</v>
+        <v>2030664</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>7136073</v>
+        <v>865069</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>8570348</v>
+        <v>9535429</v>
       </c>
     </row>
     <row r="9">
@@ -1175,100 +1175,100 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5523983</v>
+        <v>3103370</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6766698</v>
+        <v>5830622</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3237333</v>
+        <v>9412236</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4568860</v>
+        <v>7338547</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7562717</v>
+        <v>322574</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>372383</v>
+        <v>7505580</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>6404917</v>
+        <v>3991723</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9518099</v>
+        <v>9513110</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>6098531</v>
+        <v>6512282</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>4966818</v>
+        <v>5207166</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>7957229</v>
+        <v>3107296</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>6373394</v>
+        <v>4238373</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>3302130</v>
+        <v>6187251</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>8737936</v>
+        <v>6758710</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7665613</v>
+        <v>8632649</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>6690486</v>
+        <v>6748654</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>5900580</v>
+        <v>9698407</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8994163</v>
+        <v>8033467</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>5529319</v>
+        <v>7550953</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>8230622</v>
+        <v>2759553</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>5408970</v>
+        <v>724478</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>5992227</v>
+        <v>9729563</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>2192</v>
+        <v>6295592</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9466832</v>
+        <v>4601942</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>2237519</v>
+        <v>9237687</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>7693909</v>
+        <v>4483184</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>921456</v>
+        <v>3666355</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>15316</v>
+        <v>8785632</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>9929944</v>
+        <v>6379571</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>5031397</v>
+        <v>1165477</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>362144</v>
+        <v>5442366</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>6205249</v>
+        <v>8426206</v>
       </c>
     </row>
     <row r="10">
@@ -1278,100 +1278,100 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6409889</v>
+        <v>7872474</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6312456</v>
+        <v>4343410</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>961675</v>
+        <v>8646700</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4763747</v>
+        <v>4050803</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5116051</v>
+        <v>7124023</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9901133</v>
+        <v>9841151</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>6087510</v>
+        <v>7174858</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>9407991</v>
+        <v>5265170</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3276233</v>
+        <v>6872756</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>321029</v>
+        <v>8327521</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>6217498</v>
+        <v>3352562</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>244874</v>
+        <v>5049546</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>3051303</v>
+        <v>7567948</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1866035</v>
+        <v>8782194</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>2204882</v>
+        <v>3066291</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>7212044</v>
+        <v>479247</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>7818686</v>
+        <v>3607775</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>428690</v>
+        <v>2027928</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>4959858</v>
+        <v>804310</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>4849325</v>
+        <v>7017526</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>961779</v>
+        <v>2264311</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>4176177</v>
+        <v>1741526</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>9450766</v>
+        <v>2327738</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1277055</v>
+        <v>9178572</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>7263911</v>
+        <v>13392</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>312047</v>
+        <v>4859202</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>6445810</v>
+        <v>7900236</v>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>2271103</v>
+        <v>5540216</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>526256</v>
+        <v>7328615</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>6558709</v>
+        <v>719343</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>3603766</v>
+        <v>4669904</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>8834824</v>
+        <v>1505325</v>
       </c>
     </row>
     <row r="11">
@@ -1381,100 +1381,100 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9231395</v>
+        <v>3296161</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9470693</v>
+        <v>3227399</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2142096</v>
+        <v>5642131</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1204057</v>
+        <v>3682963</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7815018</v>
+        <v>4753049</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1230785</v>
+        <v>5889018</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7664463</v>
+        <v>784450</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>9803964</v>
+        <v>7141023</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3436962</v>
+        <v>6630401</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>9389044</v>
+        <v>1066202</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>5822803</v>
+        <v>6749364</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2564492</v>
+        <v>407291</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>9929199</v>
+        <v>7129539</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>3800501</v>
+        <v>2688499</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>9668271</v>
+        <v>151229</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>7620034</v>
+        <v>9455430</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>821619</v>
+        <v>6642300</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>899005</v>
+        <v>1075403</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>8891406</v>
+        <v>3545921</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>6475296</v>
+        <v>4404805</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>7628412</v>
+        <v>6178542</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>5243356</v>
+        <v>603632</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>7766611</v>
+        <v>407562</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>7668423</v>
+        <v>7791573</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5776453</v>
+        <v>8143248</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>2447772</v>
+        <v>7932332</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>6362036</v>
+        <v>6369150</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>5203321</v>
+        <v>8900240</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>6984039</v>
+        <v>2807302</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>9542503</v>
+        <v>230995</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>8131961</v>
+        <v>4021319</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>8974673</v>
+        <v>5349815</v>
       </c>
     </row>
     <row r="12">
@@ -1484,100 +1484,100 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3407306</v>
+        <v>4779443</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3908450</v>
+        <v>35620</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>8066729</v>
+        <v>9407654</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>9716364</v>
+        <v>4617876</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>6370367</v>
+        <v>1563630</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5496381</v>
+        <v>9385480</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4797010</v>
+        <v>8634534</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1613065</v>
+        <v>448936</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>8945018</v>
+        <v>1014300</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>5796027</v>
+        <v>9556951</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>8415086</v>
+        <v>51748</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>6611901</v>
+        <v>5990929</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>7152801</v>
+        <v>4833139</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>4899180</v>
+        <v>6428094</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>5145691</v>
+        <v>6347728</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>9615130</v>
+        <v>3135809</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>2643701</v>
+        <v>9894917</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>4903738</v>
+        <v>236223</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>5583567</v>
+        <v>4478259</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>400725</v>
+        <v>1802104</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>975450</v>
+        <v>3351974</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>4336356</v>
+        <v>1693465</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>8237370</v>
+        <v>9857868</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>328343</v>
+        <v>5846078</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3713676</v>
+        <v>7555500</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>6202209</v>
+        <v>5397366</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>9449473</v>
+        <v>9622446</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>8213873</v>
+        <v>2657792</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>8463247</v>
+        <v>6731070</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>9631458</v>
+        <v>3765538</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>1653307</v>
+        <v>7416726</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>9919856</v>
+        <v>1962890</v>
       </c>
     </row>
     <row r="13">
@@ -1587,100 +1587,100 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>299278</v>
+        <v>4387837</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5912078</v>
+        <v>8913895</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2186793</v>
+        <v>1256301</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>838696</v>
+        <v>4711093</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6891452</v>
+        <v>6514406</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>6467998</v>
+        <v>1674108</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4167757</v>
+        <v>5686868</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1162170</v>
+        <v>9958403</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3351979</v>
+        <v>8934268</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>3420844</v>
+        <v>7425843</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>8700432</v>
+        <v>8459523</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>9640572</v>
+        <v>8420554</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>4048693</v>
+        <v>7028525</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9902873</v>
+        <v>8093335</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>7485429</v>
+        <v>2255232</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>6806685</v>
+        <v>9509771</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>9619754</v>
+        <v>932942</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>7465019</v>
+        <v>7855666</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>9500050</v>
+        <v>9607632</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6188211</v>
+        <v>1204733</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>5658762</v>
+        <v>1959175</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>1282665</v>
+        <v>2958363</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>888623</v>
+        <v>2590493</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>1482964</v>
+        <v>6449504</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>7451083</v>
+        <v>8082</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>9185471</v>
+        <v>3031113</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>8355012</v>
+        <v>9957036</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>5035563</v>
+        <v>3187903</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>3412675</v>
+        <v>2417832</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>2522876</v>
+        <v>7968275</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>515609</v>
+        <v>5090344</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>1968755</v>
+        <v>452973</v>
       </c>
     </row>
     <row r="14">
@@ -1690,100 +1690,100 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5958327</v>
+        <v>1448491</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8518219</v>
+        <v>8745925</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3304788</v>
+        <v>2188278</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8075550</v>
+        <v>7791040</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>7668938</v>
+        <v>5793533</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>9201573</v>
+        <v>3487313</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>7356912</v>
+        <v>8743309</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>5245258</v>
+        <v>9650072</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>6335420</v>
+        <v>7766860</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>458465</v>
+        <v>7128530</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>2068698</v>
+        <v>8901914</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>3277474</v>
+        <v>6437618</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>4788328</v>
+        <v>1834738</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>2358486</v>
+        <v>3665562</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2050928</v>
+        <v>8348207</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>7391994</v>
+        <v>2250172</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>7557621</v>
+        <v>2344954</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>8231512</v>
+        <v>8604616</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>6228877</v>
+        <v>7398232</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1206486</v>
+        <v>297302</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>9814797</v>
+        <v>423849</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>3784189</v>
+        <v>2727472</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>2890950</v>
+        <v>9005333</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>9979619</v>
+        <v>1824938</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>4676740</v>
+        <v>27409</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>1098536</v>
+        <v>9327095</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>6158974</v>
+        <v>9237540</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>6343539</v>
+        <v>4479857</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>2112416</v>
+        <v>9044298</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>9448913</v>
+        <v>4065469</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>2287838</v>
+        <v>8197258</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>6937808</v>
+        <v>442101</v>
       </c>
     </row>
     <row r="15">
@@ -1793,100 +1793,100 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7408290</v>
+        <v>9621709</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>8351631</v>
+        <v>6750885</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>9796194</v>
+        <v>7209745</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7120937</v>
+        <v>3010208</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1381803</v>
+        <v>6287444</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>6011463</v>
+        <v>3232889</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>9261303</v>
+        <v>9471100</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>9497261</v>
+        <v>9045005</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5064415</v>
+        <v>7340695</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>9693479</v>
+        <v>8571896</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1282538</v>
+        <v>3595162</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>1528447</v>
+        <v>9113753</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>8611728</v>
+        <v>9895084</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>8823848</v>
+        <v>6224101</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>4286835</v>
+        <v>5173434</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2874900</v>
+        <v>1383861</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>9131022</v>
+        <v>8674497</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>9495003</v>
+        <v>3051160</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>9784613</v>
+        <v>9278422</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>7443527</v>
+        <v>9322192</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>6682909</v>
+        <v>9828483</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>5312905</v>
+        <v>4672957</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>5689937</v>
+        <v>5751775</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>4416826</v>
+        <v>4107059</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>5053617</v>
+        <v>1014175</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>5963922</v>
+        <v>8594783</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>848417</v>
+        <v>7069922</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>6793136</v>
+        <v>8024914</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>6051786</v>
+        <v>8667225</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>8443608</v>
+        <v>388163</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>811602</v>
+        <v>6711846</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>1334720</v>
+        <v>4618582</v>
       </c>
     </row>
     <row r="16">
@@ -1896,100 +1896,100 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5586563</v>
+        <v>5940237</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4683365</v>
+        <v>8859146</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5662068</v>
+        <v>7025452</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9427507</v>
+        <v>9662357</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>901851</v>
+        <v>9739906</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2514532</v>
+        <v>7095690</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>188985</v>
+        <v>7066327</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5266428</v>
+        <v>9473104</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2303700</v>
+        <v>7915166</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>8557636</v>
+        <v>4517729</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>6363443</v>
+        <v>3681857</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>3971856</v>
+        <v>6109453</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5294316</v>
+        <v>4019149</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2964509</v>
+        <v>3599323</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>6701483</v>
+        <v>5821914</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>2179989</v>
+        <v>6464868</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>5658123</v>
+        <v>9241723</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>2357734</v>
+        <v>505704</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1849896</v>
+        <v>9215626</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>829577</v>
+        <v>7283713</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>5637150</v>
+        <v>4193895</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>6243534</v>
+        <v>1596779</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>6432068</v>
+        <v>7561743</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>9435483</v>
+        <v>1142482</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>7805027</v>
+        <v>7682395</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>8569471</v>
+        <v>480779</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>7562838</v>
+        <v>2517225</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>7175505</v>
+        <v>6196397</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>1687137</v>
+        <v>1712246</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>6496285</v>
+        <v>4637672</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>9945508</v>
+        <v>56586</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>9377628</v>
+        <v>4792234</v>
       </c>
     </row>
     <row r="17">
@@ -1999,100 +1999,100 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3025939</v>
+        <v>7154842</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2118829</v>
+        <v>2274732</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>390910</v>
+        <v>4692903</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1042522</v>
+        <v>6559363</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4209162</v>
+        <v>5327757</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5883607</v>
+        <v>9670295</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>121415</v>
+        <v>7008165</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4399307</v>
+        <v>3347731</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>7086451</v>
+        <v>6329141</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>6119644</v>
+        <v>7372076</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>321512</v>
+        <v>4966708</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>5357823</v>
+        <v>6384308</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1851044</v>
+        <v>3688347</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>153524</v>
+        <v>4077358</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6272922</v>
+        <v>3439872</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>7266414</v>
+        <v>5434428</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>2112084</v>
+        <v>6159545</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>8308309</v>
+        <v>7723851</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>1502317</v>
+        <v>5730030</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>9656583</v>
+        <v>5579909</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>4306279</v>
+        <v>1779085</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>9251809</v>
+        <v>4221842</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>8977755</v>
+        <v>2890112</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1305001</v>
+        <v>9003407</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>3110764</v>
+        <v>9772271</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>9952663</v>
+        <v>510171</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>5132716</v>
+        <v>50066</v>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>6981473</v>
+        <v>7163297</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>1601985</v>
+        <v>5185963</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>4378416</v>
+        <v>3870457</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>3548943</v>
+        <v>2928384</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>38503</v>
+        <v>4081706</v>
       </c>
     </row>
     <row r="18">
@@ -2102,100 +2102,100 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>7757002</v>
+        <v>5911569</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>6284513</v>
+        <v>9501789</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2374821</v>
+        <v>5737178</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3209145</v>
+        <v>3920179</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>8401441</v>
+        <v>1603434</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>7354567</v>
+        <v>3244025</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>4674427</v>
+        <v>5497343</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4897352</v>
+        <v>9530145</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>7931935</v>
+        <v>8575420</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>4985181</v>
+        <v>1571508</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>8810343</v>
+        <v>5223459</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>5243872</v>
+        <v>5409740</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>158908</v>
+        <v>4039939</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>2030418</v>
+        <v>8158708</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>4189320</v>
+        <v>5574416</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>1158839</v>
+        <v>9770948</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>5029866</v>
+        <v>1566018</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>1450726</v>
+        <v>882408</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1443993</v>
+        <v>8580983</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1665229</v>
+        <v>7272914</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>9975812</v>
+        <v>6218878</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>1229813</v>
+        <v>6879571</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>9403073</v>
+        <v>4466123</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>7415489</v>
+        <v>5989573</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>6714618</v>
+        <v>7993627</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>8039721</v>
+        <v>6039030</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>6566647</v>
+        <v>8832621</v>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>9095888</v>
+        <v>8544901</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>1687570</v>
+        <v>9510480</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>1653000</v>
+        <v>6088185</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>5158152</v>
+        <v>5439714</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>7319729</v>
+        <v>1440356</v>
       </c>
     </row>
     <row r="19">
@@ -2205,100 +2205,100 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1837586</v>
+        <v>946255</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>8292736</v>
+        <v>2030302</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6506344</v>
+        <v>1264228</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>4073810</v>
+        <v>2157525</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1777077</v>
+        <v>9212583</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>7136454</v>
+        <v>2225370</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4394218</v>
+        <v>443970</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>428246</v>
+        <v>6646547</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>926385</v>
+        <v>6588481</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>3184588</v>
+        <v>9642246</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3250165</v>
+        <v>4596452</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>8509337</v>
+        <v>230584</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>4098398</v>
+        <v>3276354</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>4400705</v>
+        <v>9501553</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6385656</v>
+        <v>4476281</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>7892094</v>
+        <v>7548591</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>6285243</v>
+        <v>9940418</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>1655941</v>
+        <v>147264</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>416953</v>
+        <v>3767505</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>9545712</v>
+        <v>223353</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>9784587</v>
+        <v>1451789</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>3121781</v>
+        <v>4696779</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>1095634</v>
+        <v>1814348</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>9656909</v>
+        <v>8832605</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>8148959</v>
+        <v>4803533</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>5323953</v>
+        <v>7999054</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>9293879</v>
+        <v>66234</v>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>1210809</v>
+        <v>699461</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>3712975</v>
+        <v>3516796</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>1917428</v>
+        <v>5675945</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>9174646</v>
+        <v>8598267</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>4693023</v>
+        <v>3714705</v>
       </c>
     </row>
     <row r="20">
@@ -2308,100 +2308,100 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5700121</v>
+        <v>2579437</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>883976</v>
+        <v>7521541</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2352044</v>
+        <v>4320631</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>198136</v>
+        <v>6778606</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6879194</v>
+        <v>9867658</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3518439</v>
+        <v>5941773</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7695460</v>
+        <v>2088217</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2696929</v>
+        <v>4705066</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1325920</v>
+        <v>145996</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4930511</v>
+        <v>5650500</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1434651</v>
+        <v>7691268</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>8501857</v>
+        <v>4049587</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>4504809</v>
+        <v>7867013</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5376741</v>
+        <v>4467431</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>8745512</v>
+        <v>1498255</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>449549</v>
+        <v>7549855</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>5380183</v>
+        <v>4627500</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>308743</v>
+        <v>1169509</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>6820325</v>
+        <v>2355816</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4482050</v>
+        <v>9034713</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>7189354</v>
+        <v>1320969</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>1261595</v>
+        <v>2664868</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>1981028</v>
+        <v>7765663</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>5738411</v>
+        <v>4219974</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>4619629</v>
+        <v>4671506</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>9672960</v>
+        <v>2583185</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>3035183</v>
+        <v>2029457</v>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>1496771</v>
+        <v>8111418</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>6555057</v>
+        <v>6632669</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>6535953</v>
+        <v>1389765</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>2987271</v>
+        <v>8596115</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>6983865</v>
+        <v>3563483</v>
       </c>
     </row>
     <row r="21">
@@ -2411,100 +2411,100 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4196526</v>
+        <v>9165449</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6130552</v>
+        <v>3438657</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6257956</v>
+        <v>6317062</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>8902854</v>
+        <v>4822542</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1234421</v>
+        <v>939991</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3564833</v>
+        <v>1367593</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>3752660</v>
+        <v>5587941</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>7821590</v>
+        <v>5575633</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>7202790</v>
+        <v>1219596</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7690420</v>
+        <v>4508201</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>5538321</v>
+        <v>3551859</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>8119013</v>
+        <v>7028419</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>3237265</v>
+        <v>442463</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>9754202</v>
+        <v>9556262</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6291631</v>
+        <v>6522202</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>958691</v>
+        <v>9044908</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>77694</v>
+        <v>8511659</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>293086</v>
+        <v>8593077</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>4894627</v>
+        <v>4294891</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>8116674</v>
+        <v>8428826</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>6819441</v>
+        <v>9147739</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>8060775</v>
+        <v>2599137</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>318189</v>
+        <v>7180111</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>1709886</v>
+        <v>1207115</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8071574</v>
+        <v>4175768</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>2461317</v>
+        <v>2859116</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>216234</v>
+        <v>4066564</v>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>8758430</v>
+        <v>9418752</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>365377</v>
+        <v>6365857</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>7314751</v>
+        <v>8952831</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>4801998</v>
+        <v>2751111</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>1745333</v>
+        <v>91221</v>
       </c>
     </row>
     <row r="22">
@@ -2514,100 +2514,100 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7957468</v>
+        <v>9902756</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3099651</v>
+        <v>8924647</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4234081</v>
+        <v>7623454</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>486279</v>
+        <v>6520693</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6184853</v>
+        <v>6000171</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>5660677</v>
+        <v>10738</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>7549245</v>
+        <v>6332439</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4772240</v>
+        <v>3904651</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9878928</v>
+        <v>1836144</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>4320276</v>
+        <v>8203973</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>4328350</v>
+        <v>5190141</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>4968623</v>
+        <v>5044089</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>9891157</v>
+        <v>7061736</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>6484641</v>
+        <v>7213585</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>662577</v>
+        <v>425787</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>1485593</v>
+        <v>1972611</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>6186855</v>
+        <v>6657828</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>4241130</v>
+        <v>7018340</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>5448524</v>
+        <v>4128919</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>4698155</v>
+        <v>3139912</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>952582</v>
+        <v>8918277</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>811043</v>
+        <v>1313049</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2555384</v>
+        <v>4545740</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>1115620</v>
+        <v>8156173</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>375476</v>
+        <v>3334064</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>3453049</v>
+        <v>5534786</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>5615010</v>
+        <v>9397482</v>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>3954914</v>
+        <v>5831776</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>1868773</v>
+        <v>1619196</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>4724060</v>
+        <v>7086283</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>5102294</v>
+        <v>2175505</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>9998615</v>
+        <v>84980</v>
       </c>
     </row>
     <row r="23">
@@ -2617,100 +2617,100 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>9958566</v>
+        <v>9802966</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>7303459</v>
+        <v>943383</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2944237</v>
+        <v>5646719</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>9438603</v>
+        <v>2045119</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9409593</v>
+        <v>8970720</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>9725326</v>
+        <v>520846</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1717148</v>
+        <v>1056588</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3585816</v>
+        <v>5289954</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9623973</v>
+        <v>1004165</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4806356</v>
+        <v>1096238</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>5181610</v>
+        <v>9782650</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5936636</v>
+        <v>7967065</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2708395</v>
+        <v>3001470</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>7621478</v>
+        <v>6795586</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>7314527</v>
+        <v>6526122</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4611754</v>
+        <v>4963380</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>4679937</v>
+        <v>5590029</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7026014</v>
+        <v>4863977</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>5016693</v>
+        <v>5913946</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1350470</v>
+        <v>9558525</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>4790146</v>
+        <v>7075479</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>2768691</v>
+        <v>5776137</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>4397470</v>
+        <v>5392641</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>4918826</v>
+        <v>142251</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>6973287</v>
+        <v>1988761</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>440667</v>
+        <v>8456131</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>9319169</v>
+        <v>4069984</v>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>9912337</v>
+        <v>4755649</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>8351320</v>
+        <v>8337396</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>3972341</v>
+        <v>610397</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>3293540</v>
+        <v>841454</v>
       </c>
       <c r="AG23" s="3" t="n">
-        <v>4709700</v>
+        <v>1703854</v>
       </c>
     </row>
     <row r="24">
@@ -2720,100 +2720,100 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3922538</v>
+        <v>6650643</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>9871961</v>
+        <v>2572540</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>9618232</v>
+        <v>583071</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>4913727</v>
+        <v>4078761</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5514293</v>
+        <v>4336742</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>6884708</v>
+        <v>1604277</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>1204100</v>
+        <v>2675306</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>3151348</v>
+        <v>1820169</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>7071121</v>
+        <v>420556</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2675074</v>
+        <v>4773252</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1610478</v>
+        <v>4063055</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>6785928</v>
+        <v>4770655</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>6716129</v>
+        <v>2513765</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>7455890</v>
+        <v>8962444</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>9578881</v>
+        <v>1378838</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>7460052</v>
+        <v>8344575</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>7257263</v>
+        <v>8049040</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>8803884</v>
+        <v>6264296</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>169142</v>
+        <v>797884</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>9234681</v>
+        <v>961622</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>2298337</v>
+        <v>1554515</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>5049493</v>
+        <v>3394596</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>4439894</v>
+        <v>7334948</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>5852666</v>
+        <v>44958</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7198505</v>
+        <v>604472</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>9685183</v>
+        <v>1141590</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>731197</v>
+        <v>6436542</v>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>9223523</v>
+        <v>4420179</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>9944794</v>
+        <v>2952396</v>
       </c>
       <c r="AE24" s="3" t="n">
-        <v>6908649</v>
+        <v>5738471</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>9565028</v>
+        <v>2493406</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>592738</v>
+        <v>9221000</v>
       </c>
     </row>
     <row r="25">
@@ -2823,100 +2823,100 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8680157</v>
+        <v>8618536</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>9205192</v>
+        <v>4357</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1175519</v>
+        <v>273446</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6334796</v>
+        <v>330896</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>342175</v>
+        <v>9452507</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1786284</v>
+        <v>3980303</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4449431</v>
+        <v>2852018</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8435518</v>
+        <v>4150983</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2166448</v>
+        <v>5304095</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>7434303</v>
+        <v>3999550</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>3293981</v>
+        <v>7229140</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>3180173</v>
+        <v>1938823</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>8758659</v>
+        <v>5451932</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>6893331</v>
+        <v>9396610</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>4781294</v>
+        <v>2023264</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>5159089</v>
+        <v>6455088</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>5408765</v>
+        <v>6432255</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>3557480</v>
+        <v>5163868</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>4970050</v>
+        <v>4560315</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6161420</v>
+        <v>3033627</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>5601031</v>
+        <v>9488570</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>3099934</v>
+        <v>5573875</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>94231</v>
+        <v>6457031</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>3056926</v>
+        <v>1429357</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>5017467</v>
+        <v>6708657</v>
       </c>
       <c r="AA25" s="3" t="n">
-        <v>9349973</v>
+        <v>5498735</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>2485092</v>
+        <v>6650846</v>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>3889298</v>
+        <v>1644258</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>5178194</v>
+        <v>395788</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>2831294</v>
+        <v>6266499</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>3561664</v>
+        <v>9384778</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>5983311</v>
+        <v>7500494</v>
       </c>
     </row>
     <row r="26">
@@ -2926,100 +2926,100 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>929509</v>
+        <v>4199551</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3129254</v>
+        <v>5228265</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>5543367</v>
+        <v>8443910</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3647060</v>
+        <v>7758085</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>9658743</v>
+        <v>1017461</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>262954</v>
+        <v>2964200</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>5259193</v>
+        <v>3301096</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>7321625</v>
+        <v>4345463</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>5454030</v>
+        <v>568466</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>9936254</v>
+        <v>7559826</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>3932016</v>
+        <v>7872485</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1122978</v>
+        <v>338672</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>6843069</v>
+        <v>2909504</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>8263059</v>
+        <v>7848478</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>243444</v>
+        <v>1234405</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>4470473</v>
+        <v>5893352</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>4753884</v>
+        <v>5832938</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>4347257</v>
+        <v>3007151</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>9372753</v>
+        <v>3697669</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>93815</v>
+        <v>8862014</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>2178473</v>
+        <v>4461624</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>8909143</v>
+        <v>1208730</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>2377579</v>
+        <v>7989437</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>9098329</v>
+        <v>5512121</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2470095</v>
+        <v>354432</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>9852912</v>
+        <v>7663852</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>4605332</v>
+        <v>5786184</v>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>2767547</v>
+        <v>2394540</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>4801857</v>
+        <v>1971925</v>
       </c>
       <c r="AE26" s="3" t="n">
-        <v>2624088</v>
+        <v>3052629</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>2513175</v>
+        <v>5422210</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>1027676</v>
+        <v>8920714</v>
       </c>
     </row>
     <row r="27">
@@ -3029,100 +3029,100 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6413504</v>
+        <v>1180195</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1383314</v>
+        <v>3281519</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9312188</v>
+        <v>395935</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2443712</v>
+        <v>903088</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>8793423</v>
+        <v>575515</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1548662</v>
+        <v>27335</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8473061</v>
+        <v>2390463</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2049798</v>
+        <v>4622220</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4927148</v>
+        <v>2165438</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1402016</v>
+        <v>7458640</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4910123</v>
+        <v>3580275</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>8082339</v>
+        <v>2086555</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2423857</v>
+        <v>4336562</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>463737</v>
+        <v>3065030</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2563974</v>
+        <v>9950131</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4268999</v>
+        <v>818214</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>5317891</v>
+        <v>384686</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>4632291</v>
+        <v>8256383</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>1904209</v>
+        <v>5154067</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6614851</v>
+        <v>8741122</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>3737070</v>
+        <v>6676369</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>6637492</v>
+        <v>1440459</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>2296605</v>
+        <v>6808332</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>5763648</v>
+        <v>1547557</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>6519391</v>
+        <v>3705274</v>
       </c>
       <c r="AA27" s="3" t="n">
-        <v>8822183</v>
+        <v>8317332</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>98522</v>
+        <v>4855817</v>
       </c>
       <c r="AC27" s="3" t="n">
-        <v>2296606</v>
+        <v>5056547</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>2290359</v>
+        <v>7838973</v>
       </c>
       <c r="AE27" s="3" t="n">
-        <v>5666833</v>
+        <v>3718688</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>7184915</v>
+        <v>7089405</v>
       </c>
       <c r="AG27" s="3" t="n">
-        <v>5312079</v>
+        <v>257398</v>
       </c>
     </row>
     <row r="28">
@@ -3132,100 +3132,100 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2917176</v>
+        <v>657699</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1512537</v>
+        <v>2057056</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1006682</v>
+        <v>5001881</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>8459373</v>
+        <v>2912674</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>327140</v>
+        <v>327078</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4659659</v>
+        <v>7890933</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>4028510</v>
+        <v>9203680</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2976695</v>
+        <v>2352345</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5801636</v>
+        <v>5869683</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1879858</v>
+        <v>6290767</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>8678565</v>
+        <v>190845</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>7066812</v>
+        <v>6347595</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>5168198</v>
+        <v>2077885</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>6893147</v>
+        <v>8245420</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>3705974</v>
+        <v>7253884</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>783691</v>
+        <v>3569172</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>6685077</v>
+        <v>8945022</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>175724</v>
+        <v>5497128</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>7721363</v>
+        <v>7069560</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2114278</v>
+        <v>6598834</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>8690345</v>
+        <v>8799735</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>1092465</v>
+        <v>2215070</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>1806891</v>
+        <v>5693257</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>9321905</v>
+        <v>405528</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>1775937</v>
+        <v>1843834</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>3693028</v>
+        <v>5035119</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>4940938</v>
+        <v>5594407</v>
       </c>
       <c r="AC28" s="3" t="n">
-        <v>491703</v>
+        <v>6606946</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>2874816</v>
+        <v>8321199</v>
       </c>
       <c r="AE28" s="3" t="n">
-        <v>8851664</v>
+        <v>5979994</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>3803230</v>
+        <v>3750999</v>
       </c>
       <c r="AG28" s="3" t="n">
-        <v>6187995</v>
+        <v>906335</v>
       </c>
     </row>
     <row r="29">
@@ -3235,100 +3235,100 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9314248</v>
+        <v>872726</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6279843</v>
+        <v>6098880</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6352742</v>
+        <v>1749482</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4597280</v>
+        <v>5475720</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2090193</v>
+        <v>2323534</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1022094</v>
+        <v>5744660</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7287943</v>
+        <v>1101643</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>944455</v>
+        <v>2237590</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5789936</v>
+        <v>8050311</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2239532</v>
+        <v>3260186</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1759517</v>
+        <v>4655341</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>9618355</v>
+        <v>9044522</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2084362</v>
+        <v>267821</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2133127</v>
+        <v>4894869</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2375800</v>
+        <v>3754804</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>7534528</v>
+        <v>9573705</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1392451</v>
+        <v>5607049</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>7903840</v>
+        <v>9708138</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>5619609</v>
+        <v>4231693</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>6523987</v>
+        <v>357669</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>4496036</v>
+        <v>5286860</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>1808435</v>
+        <v>8979209</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>1844732</v>
+        <v>8161005</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>6381846</v>
+        <v>2579701</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6845406</v>
+        <v>2558394</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>7211729</v>
+        <v>5492071</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>4850963</v>
+        <v>6006889</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>4850056</v>
+        <v>2912090</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>7410817</v>
+        <v>2397250</v>
       </c>
       <c r="AE29" s="3" t="n">
-        <v>6627716</v>
+        <v>8754651</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>4741637</v>
+        <v>6387338</v>
       </c>
       <c r="AG29" s="3" t="n">
-        <v>2663100</v>
+        <v>9583153</v>
       </c>
     </row>
     <row r="30">
@@ -3338,100 +3338,100 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9182466</v>
+        <v>6631307</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>886431</v>
+        <v>1343601</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6209678</v>
+        <v>6049540</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1222253</v>
+        <v>955145</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4869915</v>
+        <v>1970701</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1690718</v>
+        <v>686930</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4987613</v>
+        <v>6210034</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>6961683</v>
+        <v>3874363</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>509218</v>
+        <v>3281876</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1988976</v>
+        <v>5879454</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>8499012</v>
+        <v>3854515</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>8518330</v>
+        <v>272461</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7501560</v>
+        <v>3843131</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>6185669</v>
+        <v>2934854</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1897485</v>
+        <v>6409282</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1179597</v>
+        <v>9683863</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>3210770</v>
+        <v>5001197</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>3855637</v>
+        <v>242804</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4655039</v>
+        <v>9473098</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>8875774</v>
+        <v>1704456</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>3353584</v>
+        <v>8767065</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>5841695</v>
+        <v>3901591</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>781670</v>
+        <v>4670460</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6422559</v>
+        <v>148544</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>343737</v>
+        <v>6958027</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>7425457</v>
+        <v>3952578</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>5191686</v>
+        <v>9448000</v>
       </c>
       <c r="AC30" s="3" t="n">
-        <v>391392</v>
+        <v>9633371</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>2664175</v>
+        <v>2168245</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>8216205</v>
+        <v>2051016</v>
       </c>
       <c r="AF30" s="3" t="n">
-        <v>8747829</v>
+        <v>842135</v>
       </c>
       <c r="AG30" s="3" t="n">
-        <v>8950621</v>
+        <v>3261845</v>
       </c>
     </row>
     <row r="31">
@@ -3441,100 +3441,100 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>4462358</v>
+        <v>6149000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>9425047</v>
+        <v>9403683</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1694310</v>
+        <v>8431174</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1440123</v>
+        <v>3637444</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>8855279</v>
+        <v>4251733</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>7750995</v>
+        <v>9358462</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>6765519</v>
+        <v>1296402</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>8318261</v>
+        <v>5352644</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>8215952</v>
+        <v>7292085</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>5211005</v>
+        <v>4548771</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>4345615</v>
+        <v>3873821</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>982915</v>
+        <v>5740686</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>9660680</v>
+        <v>6860644</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>2297037</v>
+        <v>1379626</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2574228</v>
+        <v>5385665</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>871072</v>
+        <v>459261</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>7529072</v>
+        <v>4389873</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>8579798</v>
+        <v>7629029</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>349313</v>
+        <v>2428324</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>7212583</v>
+        <v>7973488</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>6626385</v>
+        <v>9104748</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>6867918</v>
+        <v>5745595</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>4873960</v>
+        <v>4222895</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>843463</v>
+        <v>6075464</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>5074239</v>
+        <v>4868294</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>153964</v>
+        <v>6554427</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>3470689</v>
+        <v>4213870</v>
       </c>
       <c r="AC31" s="3" t="n">
-        <v>6227323</v>
+        <v>1093840</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>5044932</v>
+        <v>6923549</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>6331409</v>
+        <v>6306426</v>
       </c>
       <c r="AF31" s="3" t="n">
-        <v>2347117</v>
+        <v>4895890</v>
       </c>
       <c r="AG31" s="3" t="n">
-        <v>3802804</v>
+        <v>3779929</v>
       </c>
     </row>
     <row r="32">
@@ -3544,100 +3544,100 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>906488</v>
+        <v>3342135</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>7476789</v>
+        <v>2285384</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>5607679</v>
+        <v>6255733</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>6009499</v>
+        <v>6134929</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3397069</v>
+        <v>5036792</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>7481880</v>
+        <v>1726713</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>575390</v>
+        <v>6857122</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>6124381</v>
+        <v>8187069</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5498236</v>
+        <v>6775613</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3440994</v>
+        <v>3814597</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>8088713</v>
+        <v>953965</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>4709920</v>
+        <v>2486032</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2808543</v>
+        <v>8423249</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>76610</v>
+        <v>9446477</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>9925869</v>
+        <v>7978642</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>3532413</v>
+        <v>9802664</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>84688</v>
+        <v>3365139</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1540388</v>
+        <v>1062413</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>4229805</v>
+        <v>5216281</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>6728281</v>
+        <v>5870648</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>2559942</v>
+        <v>2200065</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>3192620</v>
+        <v>9616695</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>4973255</v>
+        <v>9798794</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>115712</v>
+        <v>1461256</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2641410</v>
+        <v>3601342</v>
       </c>
       <c r="AA32" s="3" t="n">
-        <v>5447680</v>
+        <v>3308783</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>1955728</v>
+        <v>788135</v>
       </c>
       <c r="AC32" s="3" t="n">
-        <v>1493079</v>
+        <v>9908889</v>
       </c>
       <c r="AD32" s="3" t="n">
-        <v>1278605</v>
+        <v>9404262</v>
       </c>
       <c r="AE32" s="3" t="n">
-        <v>8548732</v>
+        <v>8793866</v>
       </c>
       <c r="AF32" s="3" t="n">
-        <v>388063</v>
+        <v>1393198</v>
       </c>
       <c r="AG32" s="3" t="n">
-        <v>4256131</v>
+        <v>3934659</v>
       </c>
     </row>
     <row r="33">
@@ -3647,100 +3647,100 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>8452746</v>
+        <v>47189</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>5162456</v>
+        <v>6439250</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>9614497</v>
+        <v>4514099</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>6499762</v>
+        <v>3942584</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>153995</v>
+        <v>4542497</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9233076</v>
+        <v>280043</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8071506</v>
+        <v>4889983</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1704223</v>
+        <v>5907278</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>6772898</v>
+        <v>570182</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>7265578</v>
+        <v>2799799</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2317365</v>
+        <v>5509630</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>2835206</v>
+        <v>4422580</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1344826</v>
+        <v>5760610</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>6775552</v>
+        <v>8314556</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5387959</v>
+        <v>7088950</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>8861197</v>
+        <v>8234123</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>9157551</v>
+        <v>2101029</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>9559463</v>
+        <v>4785058</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>4350698</v>
+        <v>2210431</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>1654637</v>
+        <v>2501595</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>1427117</v>
+        <v>9644836</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>911572</v>
+        <v>2053045</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>8285876</v>
+        <v>8915727</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>3751543</v>
+        <v>6472379</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>8327541</v>
+        <v>4403059</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>8506904</v>
+        <v>1232051</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>4833553</v>
+        <v>2985390</v>
       </c>
       <c r="AC33" s="3" t="n">
-        <v>7165441</v>
+        <v>4582268</v>
       </c>
       <c r="AD33" s="3" t="n">
-        <v>8255609</v>
+        <v>5843957</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>5339585</v>
+        <v>5794232</v>
       </c>
       <c r="AF33" s="3" t="n">
-        <v>3407751</v>
+        <v>9540023</v>
       </c>
       <c r="AG33" s="3" t="n">
-        <v>2607238</v>
+        <v>3458158</v>
       </c>
     </row>
     <row r="34">
@@ -3750,100 +3750,100 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2970937</v>
+        <v>5258913</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>6921175</v>
+        <v>690063</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>7012478</v>
+        <v>5597853</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>5609265</v>
+        <v>9261931</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>5987226</v>
+        <v>9859502</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>4531248</v>
+        <v>2884845</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>516487</v>
+        <v>9762791</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>8047869</v>
+        <v>2578513</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8580118</v>
+        <v>4092270</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>5195642</v>
+        <v>3214246</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>6231766</v>
+        <v>2244987</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>6885467</v>
+        <v>2696403</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>4593393</v>
+        <v>896513</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8123968</v>
+        <v>8213770</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>601839</v>
+        <v>9716352</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3884072</v>
+        <v>5703679</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>1051730</v>
+        <v>2835917</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>8346788</v>
+        <v>7607757</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>6760085</v>
+        <v>4474902</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1400071</v>
+        <v>6041212</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2093141</v>
+        <v>2861231</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>2726765</v>
+        <v>6385403</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>3537643</v>
+        <v>6313997</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>9823822</v>
+        <v>9726900</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8967709</v>
+        <v>6323643</v>
       </c>
       <c r="AA34" s="3" t="n">
-        <v>31714</v>
+        <v>3569880</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>3244541</v>
+        <v>5110411</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>3348918</v>
+        <v>5984003</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>5895421</v>
+        <v>2846560</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>1403360</v>
+        <v>1610599</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>5724644</v>
+        <v>7579334</v>
       </c>
       <c r="AG34" s="3" t="n">
-        <v>2710856</v>
+        <v>3731682</v>
       </c>
     </row>
     <row r="35">
@@ -3853,100 +3853,100 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>2370753</v>
+        <v>4384797</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>5172890</v>
+        <v>2173017</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>9517861</v>
+        <v>8633534</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>5174070</v>
+        <v>1423236</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>9636405</v>
+        <v>8025704</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6468351</v>
+        <v>4041985</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>7180593</v>
+        <v>6700210</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3879617</v>
+        <v>9875947</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>8126096</v>
+        <v>4662169</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1572326</v>
+        <v>721228</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>3318356</v>
+        <v>7775115</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>2153671</v>
+        <v>2178459</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>6616322</v>
+        <v>8077381</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>559781</v>
+        <v>631069</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9973873</v>
+        <v>8615751</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>4257708</v>
+        <v>6006861</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>6757931</v>
+        <v>1867562</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>605853</v>
+        <v>1927149</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>9400470</v>
+        <v>6337381</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>5731228</v>
+        <v>9232607</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>4011923</v>
+        <v>5024666</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>3411989</v>
+        <v>3663328</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>4336577</v>
+        <v>7366209</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>443010</v>
+        <v>98844</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>7667771</v>
+        <v>7639671</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>9073846</v>
+        <v>6186553</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>4141360</v>
+        <v>8261485</v>
       </c>
       <c r="AC35" s="3" t="n">
-        <v>389653</v>
+        <v>7415500</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>1874258</v>
+        <v>8500751</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>4130141</v>
+        <v>4720272</v>
       </c>
       <c r="AF35" s="3" t="n">
-        <v>9292099</v>
+        <v>5744646</v>
       </c>
       <c r="AG35" s="3" t="n">
-        <v>7207482</v>
+        <v>320115</v>
       </c>
     </row>
   </sheetData>
@@ -4177,100 +4177,100 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9602079</v>
+        <v>1022552</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7281529</v>
+        <v>6390850</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6486852</v>
+        <v>505957</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>87119</v>
+        <v>626288</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2638479</v>
+        <v>916317</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4945220</v>
+        <v>9240496</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2533539</v>
+        <v>99168</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4778748</v>
+        <v>7366503</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>7233431</v>
+        <v>7978460</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>7989504</v>
+        <v>9637889</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5437588</v>
+        <v>3203626</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>8562977</v>
+        <v>9141943</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>6328393</v>
+        <v>9606456</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>7303165</v>
+        <v>4651318</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9210252</v>
+        <v>5558100</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>3351718</v>
+        <v>5690272</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>3233764</v>
+        <v>3875360</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>3228581</v>
+        <v>9541856</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>9349306</v>
+        <v>5330301</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>3827758</v>
+        <v>2221197</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>9690362</v>
+        <v>4248850</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>8721803</v>
+        <v>2206333</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>3430143</v>
+        <v>9112399</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>5217219</v>
+        <v>8458803</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>3653466</v>
+        <v>5985518</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>9871286</v>
+        <v>3774700</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>3146592</v>
+        <v>4248823</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>9879459</v>
+        <v>965867</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>3478188</v>
+        <v>4988415</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>9435582</v>
+        <v>339715</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>3873063</v>
+        <v>2305665</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>7632991</v>
+        <v>7232591</v>
       </c>
     </row>
     <row r="5">
@@ -4280,100 +4280,100 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9608181</v>
+        <v>8038665</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2456550</v>
+        <v>6210457</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>819768</v>
+        <v>9504377</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>8319375</v>
+        <v>5765237</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6155589</v>
+        <v>9669779</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8310952</v>
+        <v>9315983</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6709250</v>
+        <v>8853781</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>670103</v>
+        <v>9229242</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>5765474</v>
+        <v>1915749</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3087408</v>
+        <v>3462916</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>7168661</v>
+        <v>3711965</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>7553464</v>
+        <v>2570690</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4727910</v>
+        <v>7601059</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>3551550</v>
+        <v>7845936</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9316174</v>
+        <v>7922493</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>3764542</v>
+        <v>1734002</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>9767326</v>
+        <v>9637986</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>7590955</v>
+        <v>4203604</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>5096234</v>
+        <v>5611412</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6279559</v>
+        <v>1871565</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>3360191</v>
+        <v>4623891</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1484309</v>
+        <v>8859933</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>6731748</v>
+        <v>6059888</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7149653</v>
+        <v>5904987</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>747641</v>
+        <v>7640854</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>3868536</v>
+        <v>835083</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>2755228</v>
+        <v>9046828</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>8560133</v>
+        <v>4354455</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>9463309</v>
+        <v>9185820</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>8294060</v>
+        <v>3305995</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>8088193</v>
+        <v>744233</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>9595324</v>
+        <v>8164967</v>
       </c>
     </row>
     <row r="6">
@@ -4383,100 +4383,100 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7822691</v>
+        <v>3873472</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>8721237</v>
+        <v>3027496</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>9782108</v>
+        <v>5270118</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1593868</v>
+        <v>4146175</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1806058</v>
+        <v>4244120</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6636455</v>
+        <v>1539399</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6094433</v>
+        <v>945170</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>9250238</v>
+        <v>5547175</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7615663</v>
+        <v>4244212</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6790887</v>
+        <v>9727435</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>9519943</v>
+        <v>2601111</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>3056996</v>
+        <v>1968541</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>6592347</v>
+        <v>7754636</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>4271473</v>
+        <v>1598157</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8992376</v>
+        <v>415017</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>5544466</v>
+        <v>7565255</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>7221324</v>
+        <v>2953789</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7467877</v>
+        <v>9950427</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>8671208</v>
+        <v>9581267</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>9000380</v>
+        <v>7783896</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2067712</v>
+        <v>5925206</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>5841588</v>
+        <v>3054820</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>9802821</v>
+        <v>6926626</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>3943748</v>
+        <v>7464883</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9620418</v>
+        <v>3945620</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>1524936</v>
+        <v>8921571</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>8621705</v>
+        <v>3923698</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>6783080</v>
+        <v>563997</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>825583</v>
+        <v>9041281</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>5546574</v>
+        <v>4438437</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>7290592</v>
+        <v>3510485</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>7948829</v>
+        <v>8458830</v>
       </c>
     </row>
     <row r="7">
@@ -4486,100 +4486,100 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>315288</v>
+        <v>7766879</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9146337</v>
+        <v>6877452</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>36425</v>
+        <v>2428488</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4183857</v>
+        <v>5630654</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6950522</v>
+        <v>1595484</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9781582</v>
+        <v>1719728</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7503537</v>
+        <v>3017815</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8996260</v>
+        <v>6367387</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8436613</v>
+        <v>563652</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>9452880</v>
+        <v>2762705</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6516297</v>
+        <v>4518294</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>8924512</v>
+        <v>7314823</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>9210532</v>
+        <v>8736531</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>8680545</v>
+        <v>7032581</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1620462</v>
+        <v>8386638</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1938</v>
+        <v>9904338</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>9185394</v>
+        <v>3760026</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>6335713</v>
+        <v>6358651</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>7811410</v>
+        <v>9956265</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>4859509</v>
+        <v>1277198</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>523975</v>
+        <v>5003904</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>6281307</v>
+        <v>7038439</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>9382753</v>
+        <v>9927682</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>5043796</v>
+        <v>756920</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>248902</v>
+        <v>3098034</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>1833120</v>
+        <v>1143554</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>1482597</v>
+        <v>2280190</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>6897975</v>
+        <v>417369</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>1880247</v>
+        <v>9915166</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1109872</v>
+        <v>4449443</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>7062284</v>
+        <v>9996901</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>3084112</v>
+        <v>5314144</v>
       </c>
     </row>
     <row r="8">
@@ -4589,100 +4589,100 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2762408</v>
+        <v>7721897</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2368450</v>
+        <v>814684</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>7821966</v>
+        <v>1863997</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>6736140</v>
+        <v>2347797</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3409822</v>
+        <v>4805728</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>40837</v>
+        <v>4505390</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>9741202</v>
+        <v>465113</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2416759</v>
+        <v>6704965</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5868496</v>
+        <v>3072175</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>636567</v>
+        <v>822076</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>8232720</v>
+        <v>1432830</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2686316</v>
+        <v>9401857</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>6471762</v>
+        <v>5185373</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>9847325</v>
+        <v>5208815</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>4674330</v>
+        <v>9789712</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>3491645</v>
+        <v>7938846</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>642805</v>
+        <v>3845563</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>2291183</v>
+        <v>3788004</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>4878047</v>
+        <v>2927327</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>952564</v>
+        <v>2294523</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1108194</v>
+        <v>4723031</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>5792663</v>
+        <v>1592355</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>4124032</v>
+        <v>1646773</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>5539454</v>
+        <v>3020044</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>560285</v>
+        <v>9890278</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>1538425</v>
+        <v>776711</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>7644409</v>
+        <v>2807895</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>2719289</v>
+        <v>9083407</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>3546027</v>
+        <v>390735</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>2571628</v>
+        <v>5208167</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>4579290</v>
+        <v>61836</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>8431857</v>
+        <v>997887</v>
       </c>
     </row>
     <row r="9">
@@ -4692,100 +4692,100 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3227522</v>
+        <v>6192989</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4786129</v>
+        <v>3810205</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3731789</v>
+        <v>413245</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7981723</v>
+        <v>9468300</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>8995821</v>
+        <v>5658178</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6708710</v>
+        <v>5090812</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1871405</v>
+        <v>9682975</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>6700488</v>
+        <v>1662264</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>691375</v>
+        <v>4195267</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>4569859</v>
+        <v>1562552</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>7583770</v>
+        <v>9704184</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>7467274</v>
+        <v>2253028</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>7588521</v>
+        <v>3544607</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>2663831</v>
+        <v>2646503</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7244732</v>
+        <v>9132382</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>2009341</v>
+        <v>3635427</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>8703893</v>
+        <v>5038111</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>7286190</v>
+        <v>784727</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>5407117</v>
+        <v>3492368</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>9966532</v>
+        <v>787443</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>7766700</v>
+        <v>7871524</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>3470726</v>
+        <v>6540156</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>9183744</v>
+        <v>8617712</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>4137912</v>
+        <v>4028243</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>9579357</v>
+        <v>8877764</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>3263486</v>
+        <v>9646171</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>7622075</v>
+        <v>1327532</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>2317693</v>
+        <v>3421219</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>9711357</v>
+        <v>8085502</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>5653891</v>
+        <v>9094712</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>6816232</v>
+        <v>6379022</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>1105501</v>
+        <v>6413378</v>
       </c>
     </row>
     <row r="10">
@@ -4795,100 +4795,100 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6022076</v>
+        <v>979621</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6465922</v>
+        <v>8275288</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7723946</v>
+        <v>2398476</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5381559</v>
+        <v>9259216</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2945634</v>
+        <v>2304639</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1715773</v>
+        <v>7262374</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1018556</v>
+        <v>7040224</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8266739</v>
+        <v>5794485</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8579189</v>
+        <v>8637487</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>4308885</v>
+        <v>229726</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8977408</v>
+        <v>9879185</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>4449658</v>
+        <v>9784106</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2187499</v>
+        <v>9053492</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>4772947</v>
+        <v>3208520</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>3124082</v>
+        <v>3737012</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>9134389</v>
+        <v>4855871</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>9246804</v>
+        <v>9760669</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>2815723</v>
+        <v>1363973</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>3314382</v>
+        <v>6515930</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>2916861</v>
+        <v>1403228</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>8971214</v>
+        <v>9631866</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>5405913</v>
+        <v>7988946</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>3091286</v>
+        <v>9640651</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>3283054</v>
+        <v>6794229</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>3644123</v>
+        <v>1305583</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>9723608</v>
+        <v>7066641</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>6459178</v>
+        <v>778299</v>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>13697</v>
+        <v>865095</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>3496883</v>
+        <v>1162051</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>2259171</v>
+        <v>2184935</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>5290453</v>
+        <v>5565308</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>1438593</v>
+        <v>3371914</v>
       </c>
     </row>
     <row r="11">
@@ -4898,100 +4898,100 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5911925</v>
+        <v>5453256</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9155076</v>
+        <v>1499923</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2491454</v>
+        <v>9374492</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4602567</v>
+        <v>5940212</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2042394</v>
+        <v>4505655</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4759071</v>
+        <v>5564748</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>9160769</v>
+        <v>3932746</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>9163284</v>
+        <v>6003615</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>2497150</v>
+        <v>854653</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1735578</v>
+        <v>8673228</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>7287993</v>
+        <v>7429689</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>3137270</v>
+        <v>8054769</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1806287</v>
+        <v>5860860</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>165779</v>
+        <v>1943114</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>452031</v>
+        <v>3912400</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6656811</v>
+        <v>5307292</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>9989970</v>
+        <v>3276903</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>5237233</v>
+        <v>6745370</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>4663667</v>
+        <v>6893238</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>4886125</v>
+        <v>8204911</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>6247950</v>
+        <v>451146</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>3858721</v>
+        <v>4677329</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>9075000</v>
+        <v>8142735</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>9754900</v>
+        <v>2425832</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>4776800</v>
+        <v>3745585</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>4023057</v>
+        <v>794270</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>6164517</v>
+        <v>55101</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>939777</v>
+        <v>8359082</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>1391116</v>
+        <v>4918982</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>5898920</v>
+        <v>8306258</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>1840499</v>
+        <v>5046284</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>7020778</v>
+        <v>5760742</v>
       </c>
     </row>
     <row r="12">
@@ -5001,100 +5001,100 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>697722</v>
+        <v>2374333</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3654748</v>
+        <v>5461180</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2512530</v>
+        <v>2268533</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>6763606</v>
+        <v>8104738</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4746996</v>
+        <v>3198759</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4310457</v>
+        <v>6103095</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7319895</v>
+        <v>8230251</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5088125</v>
+        <v>1504965</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>8727030</v>
+        <v>2188233</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>869750</v>
+        <v>9886670</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>7164705</v>
+        <v>151140</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>5102315</v>
+        <v>8271245</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2270223</v>
+        <v>6882960</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>5311675</v>
+        <v>2470781</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>6012083</v>
+        <v>3005254</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>1461548</v>
+        <v>4671866</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>7929367</v>
+        <v>9595050</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>963093</v>
+        <v>3304501</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>9098159</v>
+        <v>3536908</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5114912</v>
+        <v>3639058</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>3861214</v>
+        <v>1684931</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>8119166</v>
+        <v>2507363</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>1170980</v>
+        <v>3082816</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>9831594</v>
+        <v>4341803</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>2431279</v>
+        <v>7443961</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>5712577</v>
+        <v>6003503</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>1839387</v>
+        <v>5721020</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>6900471</v>
+        <v>9239941</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>2017955</v>
+        <v>6575078</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>7831763</v>
+        <v>389893</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>7805662</v>
+        <v>7087017</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>7548539</v>
+        <v>4863903</v>
       </c>
     </row>
     <row r="13">
@@ -5104,100 +5104,100 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>980796</v>
+        <v>517239</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3318402</v>
+        <v>7299172</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>9589321</v>
+        <v>1205007</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6959941</v>
+        <v>8255733</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>8576228</v>
+        <v>4386951</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8675628</v>
+        <v>9542655</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>8048586</v>
+        <v>5574691</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>8954630</v>
+        <v>387679</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>206729</v>
+        <v>491442</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>2717116</v>
+        <v>617203</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>7908753</v>
+        <v>1313416</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>593534</v>
+        <v>9291943</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>9817380</v>
+        <v>7554630</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>3107718</v>
+        <v>6242548</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>3547127</v>
+        <v>6478816</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>3141017</v>
+        <v>5414011</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>616629</v>
+        <v>2565515</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>3917235</v>
+        <v>2250648</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>146476</v>
+        <v>9737318</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3073075</v>
+        <v>864891</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>5963161</v>
+        <v>9732711</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>9280857</v>
+        <v>4319886</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>8568052</v>
+        <v>4775483</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>1745123</v>
+        <v>4492620</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>7089906</v>
+        <v>257789</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>7193224</v>
+        <v>5939885</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>4498667</v>
+        <v>3728160</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>9939970</v>
+        <v>6216898</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>520719</v>
+        <v>1309680</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>505353</v>
+        <v>4945608</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>9712180</v>
+        <v>6064737</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>7232153</v>
+        <v>2529791</v>
       </c>
     </row>
     <row r="14">
@@ -5207,100 +5207,100 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2040344</v>
+        <v>745969</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>9750610</v>
+        <v>8791720</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>6393725</v>
+        <v>2754710</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1876458</v>
+        <v>6523035</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>9022525</v>
+        <v>8193859</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4841582</v>
+        <v>1713933</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>286475</v>
+        <v>8425402</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>7129865</v>
+        <v>7086817</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>4780462</v>
+        <v>7778078</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>6542492</v>
+        <v>4342600</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>9498768</v>
+        <v>1749574</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>7001147</v>
+        <v>1749699</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1177976</v>
+        <v>5466942</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>7200873</v>
+        <v>9749222</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>4984788</v>
+        <v>7960882</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>547562</v>
+        <v>7587626</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>5592111</v>
+        <v>3805539</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>4235443</v>
+        <v>8129934</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>1380948</v>
+        <v>6077958</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>2426404</v>
+        <v>3802020</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>9329455</v>
+        <v>8621591</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>9854499</v>
+        <v>4898897</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>8639681</v>
+        <v>468081</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>3179270</v>
+        <v>7328880</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8741952</v>
+        <v>5111604</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>9366555</v>
+        <v>6221751</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>2226400</v>
+        <v>2442688</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>7321981</v>
+        <v>2093173</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>4595224</v>
+        <v>5757779</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>437859</v>
+        <v>7071823</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>1063889</v>
+        <v>2743814</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>5786679</v>
+        <v>7630736</v>
       </c>
     </row>
     <row r="15">
@@ -5310,100 +5310,100 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4774652</v>
+        <v>5775488</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5010668</v>
+        <v>681682</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>9550888</v>
+        <v>826550</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7098405</v>
+        <v>9890538</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3545134</v>
+        <v>9276659</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>7327545</v>
+        <v>4248761</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>8707458</v>
+        <v>8413691</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4355237</v>
+        <v>9893250</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>9084309</v>
+        <v>4153238</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>9699309</v>
+        <v>8447685</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>9334065</v>
+        <v>1972065</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>6526914</v>
+        <v>6525728</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1406366</v>
+        <v>8544084</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>5886914</v>
+        <v>3250634</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>3541653</v>
+        <v>1782968</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>1862893</v>
+        <v>6578829</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>497346</v>
+        <v>278282</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>4170573</v>
+        <v>3994939</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>7443631</v>
+        <v>451101</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>2126329</v>
+        <v>5582613</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>8869422</v>
+        <v>4405252</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>3081942</v>
+        <v>8241959</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>4224103</v>
+        <v>6497631</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>8253964</v>
+        <v>3757361</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>4608444</v>
+        <v>1558764</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>736612</v>
+        <v>4761451</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>976529</v>
+        <v>2168568</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>7561038</v>
+        <v>4262959</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>1400458</v>
+        <v>6716702</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>5422240</v>
+        <v>1865235</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>462074</v>
+        <v>7769722</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>5733990</v>
+        <v>5309213</v>
       </c>
     </row>
     <row r="16">
@@ -5413,100 +5413,100 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9467629</v>
+        <v>7921176</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8920539</v>
+        <v>7511008</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2290592</v>
+        <v>9787329</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6558198</v>
+        <v>6050777</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3387254</v>
+        <v>456637</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>963269</v>
+        <v>8649783</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9796366</v>
+        <v>7947118</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>501826</v>
+        <v>3204365</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>7589320</v>
+        <v>2592022</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6072613</v>
+        <v>7752459</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1427448</v>
+        <v>6027953</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2074676</v>
+        <v>4294777</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4565163</v>
+        <v>8590584</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9740383</v>
+        <v>1300488</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4835438</v>
+        <v>3074302</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>9946752</v>
+        <v>7220306</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1330476</v>
+        <v>278534</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>9386702</v>
+        <v>9146219</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>3356373</v>
+        <v>9565960</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>7107112</v>
+        <v>1975768</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2123352</v>
+        <v>5001735</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>2277043</v>
+        <v>5931702</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1811639</v>
+        <v>8581813</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>9926545</v>
+        <v>7839730</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>656094</v>
+        <v>9844340</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>8295328</v>
+        <v>9040792</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>5811542</v>
+        <v>1460272</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>4536224</v>
+        <v>1701274</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>5080638</v>
+        <v>2037851</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>1036607</v>
+        <v>6951911</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>3375913</v>
+        <v>9352589</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>8539368</v>
+        <v>4457013</v>
       </c>
     </row>
     <row r="17">
@@ -5516,100 +5516,100 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2886089</v>
+        <v>3607275</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4127791</v>
+        <v>9466855</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3724224</v>
+        <v>2555896</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>315999</v>
+        <v>8614055</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>8514627</v>
+        <v>943148</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3447078</v>
+        <v>5691138</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>6115982</v>
+        <v>637897</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9020002</v>
+        <v>1804737</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>947967</v>
+        <v>3312465</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>2707668</v>
+        <v>4377149</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>4917392</v>
+        <v>7636872</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>5564896</v>
+        <v>8626339</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>6549764</v>
+        <v>2665068</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>4623615</v>
+        <v>135351</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8328659</v>
+        <v>6718941</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>7321824</v>
+        <v>4808695</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>6470666</v>
+        <v>1208949</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>4984579</v>
+        <v>9638267</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>4279539</v>
+        <v>4861224</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>6582865</v>
+        <v>8069624</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>2132726</v>
+        <v>1850626</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>5352963</v>
+        <v>672243</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>1161991</v>
+        <v>3419673</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>9765896</v>
+        <v>8066854</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6381569</v>
+        <v>7519415</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>4639987</v>
+        <v>2145390</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>2215107</v>
+        <v>5205932</v>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>6913985</v>
+        <v>2848499</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>3995138</v>
+        <v>3370610</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>4031145</v>
+        <v>8597097</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>3829131</v>
+        <v>2259553</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>3560437</v>
+        <v>8436016</v>
       </c>
     </row>
     <row r="18">
@@ -5619,100 +5619,100 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>7340975</v>
+        <v>6112319</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>6839718</v>
+        <v>6928242</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4113357</v>
+        <v>8462332</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>4231557</v>
+        <v>9815506</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9855079</v>
+        <v>4340224</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>5560885</v>
+        <v>4674248</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>4766611</v>
+        <v>4878262</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>9259241</v>
+        <v>3438203</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3645809</v>
+        <v>1933248</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>6981564</v>
+        <v>4851389</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>5354180</v>
+        <v>5089656</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>8574546</v>
+        <v>617050</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>8036628</v>
+        <v>4538243</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>7587349</v>
+        <v>5558017</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>7840090</v>
+        <v>8355815</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>5795832</v>
+        <v>3552763</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>4606652</v>
+        <v>4129717</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>8138429</v>
+        <v>8779265</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>3448946</v>
+        <v>3029169</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>6451859</v>
+        <v>5462196</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>1530365</v>
+        <v>8776511</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>2416589</v>
+        <v>1665661</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>7322888</v>
+        <v>8418781</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>8733856</v>
+        <v>7744145</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>7918214</v>
+        <v>7542625</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>3255029</v>
+        <v>609927</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>6317427</v>
+        <v>7231859</v>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>6879300</v>
+        <v>6734944</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>2175159</v>
+        <v>4713786</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>4512272</v>
+        <v>7547003</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>709734</v>
+        <v>4633237</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>2463409</v>
+        <v>3394381</v>
       </c>
     </row>
     <row r="19">
@@ -5722,100 +5722,100 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>6552032</v>
+        <v>4125600</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1175014</v>
+        <v>5124580</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>5052867</v>
+        <v>2006773</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8299051</v>
+        <v>4960300</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>7936810</v>
+        <v>4701356</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8285765</v>
+        <v>425237</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4395784</v>
+        <v>6495024</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>6393981</v>
+        <v>8983193</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>357272</v>
+        <v>5954445</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>9049475</v>
+        <v>2361852</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>4183651</v>
+        <v>8847323</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>9663414</v>
+        <v>1358243</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>4734299</v>
+        <v>5919572</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>7242054</v>
+        <v>3944711</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>4540587</v>
+        <v>2559878</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>8129663</v>
+        <v>4750759</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>8704487</v>
+        <v>9504300</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>2028107</v>
+        <v>4635154</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>8579281</v>
+        <v>1874072</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>224290</v>
+        <v>9774503</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>5781341</v>
+        <v>5859118</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>690726</v>
+        <v>1935130</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>2026476</v>
+        <v>5566055</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>6572651</v>
+        <v>3207314</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>404626</v>
+        <v>263707</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>8072490</v>
+        <v>2165478</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>2746581</v>
+        <v>4062129</v>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>7628992</v>
+        <v>5243059</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>7351604</v>
+        <v>6750068</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>7613601</v>
+        <v>6966350</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>2081005</v>
+        <v>792650</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>6360864</v>
+        <v>8703830</v>
       </c>
     </row>
     <row r="20">
@@ -5825,100 +5825,100 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>333420</v>
+        <v>7758968</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1165963</v>
+        <v>6417108</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9743114</v>
+        <v>8184724</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5586424</v>
+        <v>8506308</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1279172</v>
+        <v>973509</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5490040</v>
+        <v>214753</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6849469</v>
+        <v>9170078</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>6784291</v>
+        <v>339424</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2175878</v>
+        <v>137541</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>423290</v>
+        <v>2650597</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4004468</v>
+        <v>3583885</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>8580663</v>
+        <v>6696113</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1526062</v>
+        <v>4120856</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>4318406</v>
+        <v>7035749</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>7058348</v>
+        <v>9045968</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>4578681</v>
+        <v>3611668</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2247649</v>
+        <v>6200830</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>3181419</v>
+        <v>2512127</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>4320874</v>
+        <v>1025179</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>2926829</v>
+        <v>2716213</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>5385171</v>
+        <v>8271402</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>8195004</v>
+        <v>187342</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>1196016</v>
+        <v>429154</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>7222650</v>
+        <v>384780</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9430101</v>
+        <v>2207242</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>3574364</v>
+        <v>7914941</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>1705314</v>
+        <v>2247227</v>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>3885924</v>
+        <v>3049531</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>2104686</v>
+        <v>7774891</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>1253357</v>
+        <v>1188430</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>2009533</v>
+        <v>3638007</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>9672707</v>
+        <v>9833462</v>
       </c>
     </row>
     <row r="21">
@@ -5928,100 +5928,100 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4808831</v>
+        <v>3952997</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>7353329</v>
+        <v>211052</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>633072</v>
+        <v>1788769</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1589579</v>
+        <v>251630</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>8639269</v>
+        <v>4898021</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2583834</v>
+        <v>3693184</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>472088</v>
+        <v>7640602</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1938670</v>
+        <v>1238657</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4811524</v>
+        <v>121869</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>389864</v>
+        <v>9774668</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>5383723</v>
+        <v>5345550</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>7920158</v>
+        <v>484350</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>8358342</v>
+        <v>3775953</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>6580112</v>
+        <v>8567172</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>3476594</v>
+        <v>4225801</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>7060579</v>
+        <v>8246957</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>7033311</v>
+        <v>2995768</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>3351998</v>
+        <v>2415967</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>7603921</v>
+        <v>863</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>7532329</v>
+        <v>3631981</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>2101080</v>
+        <v>1756637</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>6324657</v>
+        <v>2835342</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>8468910</v>
+        <v>5987278</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>1663110</v>
+        <v>1042737</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>6059011</v>
+        <v>2435184</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>3837057</v>
+        <v>6351050</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>2764200</v>
+        <v>502999</v>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>4834912</v>
+        <v>4520433</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>4346334</v>
+        <v>1850067</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>6737071</v>
+        <v>7505701</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>6870468</v>
+        <v>6744887</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>143061</v>
+        <v>5259280</v>
       </c>
     </row>
     <row r="22">
@@ -6031,100 +6031,100 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>3608413</v>
+        <v>2285536</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6846572</v>
+        <v>3674114</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2494508</v>
+        <v>5579431</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>8967502</v>
+        <v>894445</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3071554</v>
+        <v>4256302</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8839491</v>
+        <v>900807</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>5558744</v>
+        <v>6035040</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>5779904</v>
+        <v>1762315</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7171833</v>
+        <v>5787394</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>7916007</v>
+        <v>7052741</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>774270</v>
+        <v>2519053</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>5910867</v>
+        <v>6170589</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>5815324</v>
+        <v>6041020</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>5479033</v>
+        <v>4159556</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>4465138</v>
+        <v>4005215</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>4221659</v>
+        <v>5956949</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>7480654</v>
+        <v>5782426</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>7393342</v>
+        <v>453074</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>5301725</v>
+        <v>8891770</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>7041494</v>
+        <v>9373742</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>5517637</v>
+        <v>3989489</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>9891127</v>
+        <v>8459910</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2508562</v>
+        <v>8701316</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>6405982</v>
+        <v>505504</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>9734890</v>
+        <v>4935706</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>3828177</v>
+        <v>7811404</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>8148397</v>
+        <v>4292396</v>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>6783850</v>
+        <v>2849178</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>2880024</v>
+        <v>9819603</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>4085074</v>
+        <v>9256771</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>2316486</v>
+        <v>9764858</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>7358346</v>
+        <v>3107796</v>
       </c>
     </row>
     <row r="23">
@@ -6134,100 +6134,100 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3148208</v>
+        <v>4503355</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5130716</v>
+        <v>3009668</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6543778</v>
+        <v>2258587</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>8331493</v>
+        <v>4078985</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>374431</v>
+        <v>9885416</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3926048</v>
+        <v>1499345</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3356889</v>
+        <v>4728292</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8972956</v>
+        <v>5105339</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1854143</v>
+        <v>2265715</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5184814</v>
+        <v>8171939</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2592137</v>
+        <v>7812431</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2457522</v>
+        <v>8750333</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>6090433</v>
+        <v>657636</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>8153782</v>
+        <v>1582168</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>209317</v>
+        <v>7153854</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>8565287</v>
+        <v>912291</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>786775</v>
+        <v>1452397</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1390686</v>
+        <v>5660610</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>1161355</v>
+        <v>524174</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>859142</v>
+        <v>6878138</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>4770013</v>
+        <v>9525965</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>5276526</v>
+        <v>9495464</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>7673624</v>
+        <v>4226992</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>5095622</v>
+        <v>8221109</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>4369047</v>
+        <v>8830856</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>71308</v>
+        <v>1550934</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>207964</v>
+        <v>6494992</v>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>8637196</v>
+        <v>8296216</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>8409303</v>
+        <v>7245194</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>8953851</v>
+        <v>8652104</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>5725731</v>
+        <v>2179926</v>
       </c>
       <c r="AG23" s="3" t="n">
-        <v>2417674</v>
+        <v>5865899</v>
       </c>
     </row>
     <row r="24">
@@ -6237,100 +6237,100 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1515974</v>
+        <v>232785</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>800564</v>
+        <v>4810137</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4227027</v>
+        <v>9582563</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>3467742</v>
+        <v>1646327</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>9244629</v>
+        <v>6417425</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>6416486</v>
+        <v>2993333</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>3007781</v>
+        <v>2798812</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8029582</v>
+        <v>2349794</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2503989</v>
+        <v>4878526</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>295922</v>
+        <v>6398140</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1572913</v>
+        <v>6773938</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>8600096</v>
+        <v>2029524</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2891044</v>
+        <v>617139</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>990593</v>
+        <v>8365563</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>6363841</v>
+        <v>6531011</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>4442428</v>
+        <v>5707769</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>2449483</v>
+        <v>1080687</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>3046305</v>
+        <v>1702297</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>3426292</v>
+        <v>8795878</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1780659</v>
+        <v>7371352</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>4858617</v>
+        <v>2391131</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>3398460</v>
+        <v>586066</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>5180351</v>
+        <v>3147255</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>7859393</v>
+        <v>5539693</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>966393</v>
+        <v>8985357</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>5214872</v>
+        <v>1348142</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>4359278</v>
+        <v>9383271</v>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>7370362</v>
+        <v>3396763</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>6884892</v>
+        <v>1908523</v>
       </c>
       <c r="AE24" s="3" t="n">
-        <v>4981386</v>
+        <v>5042526</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>8878401</v>
+        <v>5988839</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>6035508</v>
+        <v>971136</v>
       </c>
     </row>
     <row r="25">
@@ -6340,100 +6340,100 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9527626</v>
+        <v>8659900</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>5830240</v>
+        <v>2360126</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>7553475</v>
+        <v>9850849</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>8351247</v>
+        <v>1113199</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3597680</v>
+        <v>8867146</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8532302</v>
+        <v>8149864</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>289481</v>
+        <v>9413921</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2046784</v>
+        <v>7548423</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>7245482</v>
+        <v>5279502</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>574757</v>
+        <v>9877040</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>2399060</v>
+        <v>1204743</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>6698027</v>
+        <v>9165221</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1243504</v>
+        <v>6859547</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>6461677</v>
+        <v>8870631</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>507364</v>
+        <v>2246259</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>9913503</v>
+        <v>3087722</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>6480650</v>
+        <v>9779760</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>2910696</v>
+        <v>7949816</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>1323708</v>
+        <v>1183181</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1613523</v>
+        <v>1888871</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>512942</v>
+        <v>3664507</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>4399885</v>
+        <v>5819392</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>4386803</v>
+        <v>7369555</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1873914</v>
+        <v>9670062</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2774213</v>
+        <v>3417965</v>
       </c>
       <c r="AA25" s="3" t="n">
-        <v>8792747</v>
+        <v>9596100</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>3894527</v>
+        <v>3133633</v>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>345711</v>
+        <v>3342386</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>9074941</v>
+        <v>6192745</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>6132329</v>
+        <v>6723701</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>1965509</v>
+        <v>696038</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>6316426</v>
+        <v>3223072</v>
       </c>
     </row>
     <row r="26">
@@ -6443,100 +6443,100 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8815104</v>
+        <v>1798004</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>7957973</v>
+        <v>7449665</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3858222</v>
+        <v>1504465</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1926267</v>
+        <v>9990547</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>4134014</v>
+        <v>642772</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8784177</v>
+        <v>2767412</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3197734</v>
+        <v>1179845</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>7733728</v>
+        <v>1191948</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2704703</v>
+        <v>4212083</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2544534</v>
+        <v>9855020</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>4070968</v>
+        <v>2488623</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8044812</v>
+        <v>5250922</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1953380</v>
+        <v>3293427</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>7496858</v>
+        <v>5855830</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>862103</v>
+        <v>6680014</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>5765522</v>
+        <v>3392099</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>8517417</v>
+        <v>7773401</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>340324</v>
+        <v>642693</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>4645348</v>
+        <v>8272365</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>8238890</v>
+        <v>5966515</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>9937531</v>
+        <v>8448621</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>1565527</v>
+        <v>7664179</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>8058165</v>
+        <v>311433</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>1700062</v>
+        <v>5637353</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>9897110</v>
+        <v>5748792</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>7664374</v>
+        <v>8508937</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>4365454</v>
+        <v>2324070</v>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>3489048</v>
+        <v>5639280</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>5703558</v>
+        <v>4390970</v>
       </c>
       <c r="AE26" s="3" t="n">
-        <v>9549113</v>
+        <v>5027246</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>8392603</v>
+        <v>5330854</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>719103</v>
+        <v>8436543</v>
       </c>
     </row>
     <row r="27">
@@ -6546,100 +6546,100 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3362699</v>
+        <v>6650265</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8994178</v>
+        <v>3927039</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7785379</v>
+        <v>5717801</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4745090</v>
+        <v>9508295</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3955373</v>
+        <v>7812918</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1720991</v>
+        <v>54342</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2309508</v>
+        <v>2041475</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1951107</v>
+        <v>2237644</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>7736287</v>
+        <v>400802</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>214908</v>
+        <v>4451606</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>9407580</v>
+        <v>2288639</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>6758456</v>
+        <v>5665560</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2659021</v>
+        <v>3454409</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4378462</v>
+        <v>7156160</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9740490</v>
+        <v>9525740</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2132973</v>
+        <v>1174662</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1869697</v>
+        <v>2500723</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>8867579</v>
+        <v>1363404</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>90748</v>
+        <v>6264224</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>9146859</v>
+        <v>9027317</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>5685037</v>
+        <v>4929720</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>8914351</v>
+        <v>2386959</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>1232727</v>
+        <v>3544168</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>6787903</v>
+        <v>8645062</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>6850864</v>
+        <v>8400784</v>
       </c>
       <c r="AA27" s="3" t="n">
-        <v>1559278</v>
+        <v>2457044</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>2918379</v>
+        <v>8658740</v>
       </c>
       <c r="AC27" s="3" t="n">
-        <v>2327953</v>
+        <v>9746360</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>4364600</v>
+        <v>3029251</v>
       </c>
       <c r="AE27" s="3" t="n">
-        <v>9260099</v>
+        <v>3318477</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>9555483</v>
+        <v>7267351</v>
       </c>
       <c r="AG27" s="3" t="n">
-        <v>5858472</v>
+        <v>4317602</v>
       </c>
     </row>
     <row r="28">
@@ -6649,100 +6649,100 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>4107419</v>
+        <v>4382191</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4300080</v>
+        <v>4830448</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1800982</v>
+        <v>1352304</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4489108</v>
+        <v>167352</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5025149</v>
+        <v>9956243</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4967207</v>
+        <v>3388224</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>4564981</v>
+        <v>6903686</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>562456</v>
+        <v>3992827</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>4047154</v>
+        <v>2850055</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>8416884</v>
+        <v>3294284</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>3938305</v>
+        <v>322355</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>6525798</v>
+        <v>6962838</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>307962</v>
+        <v>5885392</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1478175</v>
+        <v>5514842</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>6627841</v>
+        <v>2806102</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>6731335</v>
+        <v>9121649</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>4835210</v>
+        <v>1383078</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>7802777</v>
+        <v>9337583</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>7098365</v>
+        <v>9283567</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>9659281</v>
+        <v>7179211</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>7872313</v>
+        <v>7515211</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>3998243</v>
+        <v>1945017</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>7086678</v>
+        <v>5924059</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>7560674</v>
+        <v>6739553</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>1614723</v>
+        <v>8210306</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>8913043</v>
+        <v>3060932</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>7365126</v>
+        <v>5934229</v>
       </c>
       <c r="AC28" s="3" t="n">
-        <v>5628497</v>
+        <v>534670</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>8614000</v>
+        <v>6499471</v>
       </c>
       <c r="AE28" s="3" t="n">
-        <v>5036405</v>
+        <v>6616540</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>1291208</v>
+        <v>8788813</v>
       </c>
       <c r="AG28" s="3" t="n">
-        <v>4062695</v>
+        <v>1764331</v>
       </c>
     </row>
     <row r="29">
@@ -6752,100 +6752,100 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3316844</v>
+        <v>1510869</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3516499</v>
+        <v>1000339</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3033676</v>
+        <v>6512985</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>8772474</v>
+        <v>6766481</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2276932</v>
+        <v>6986762</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>702068</v>
+        <v>4117205</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7704672</v>
+        <v>2687624</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4275670</v>
+        <v>6790443</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>7904073</v>
+        <v>8082826</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3319530</v>
+        <v>1262623</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>9927999</v>
+        <v>1408151</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>5973423</v>
+        <v>4942867</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>9930246</v>
+        <v>8811948</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>7073502</v>
+        <v>5358507</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2817793</v>
+        <v>716057</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>9274754</v>
+        <v>4485830</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>5099813</v>
+        <v>2539968</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>2501720</v>
+        <v>6044810</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>5644900</v>
+        <v>3996273</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>8254807</v>
+        <v>8286700</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>9158319</v>
+        <v>8057647</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>7978410</v>
+        <v>211481</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>3828107</v>
+        <v>2733548</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>607382</v>
+        <v>8537929</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>7765105</v>
+        <v>9503258</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>3965026</v>
+        <v>4211483</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>961310</v>
+        <v>5870132</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>1297623</v>
+        <v>2520263</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>3573924</v>
+        <v>3479246</v>
       </c>
       <c r="AE29" s="3" t="n">
-        <v>4664887</v>
+        <v>9575723</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>8064089</v>
+        <v>5897339</v>
       </c>
       <c r="AG29" s="3" t="n">
-        <v>1715572</v>
+        <v>1982715</v>
       </c>
     </row>
     <row r="30">
@@ -6855,100 +6855,100 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1517833</v>
+        <v>253148</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>924645</v>
+        <v>2629662</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>7319707</v>
+        <v>492251</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4799039</v>
+        <v>9995011</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1674828</v>
+        <v>8014179</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2174898</v>
+        <v>6760051</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>625858</v>
+        <v>3738441</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>7361116</v>
+        <v>749366</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>608588</v>
+        <v>9225771</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>9021657</v>
+        <v>4509649</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>595300</v>
+        <v>8189884</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>3919272</v>
+        <v>6143416</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1460998</v>
+        <v>4525051</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>9205970</v>
+        <v>3951965</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>3011776</v>
+        <v>4588317</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>705841</v>
+        <v>1719259</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>2762623</v>
+        <v>5489357</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>8100065</v>
+        <v>6715355</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>7790665</v>
+        <v>2099851</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1421083</v>
+        <v>8315935</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>2658476</v>
+        <v>7108989</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>2891748</v>
+        <v>7448355</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>2916578</v>
+        <v>3761031</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>7219567</v>
+        <v>6961961</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>6661087</v>
+        <v>960256</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>9753716</v>
+        <v>3445344</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>5133397</v>
+        <v>4277936</v>
       </c>
       <c r="AC30" s="3" t="n">
-        <v>8386336</v>
+        <v>7209043</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>8813712</v>
+        <v>2087820</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>6811194</v>
+        <v>3166770</v>
       </c>
       <c r="AF30" s="3" t="n">
-        <v>2945080</v>
+        <v>4851130</v>
       </c>
       <c r="AG30" s="3" t="n">
-        <v>6742603</v>
+        <v>1378687</v>
       </c>
     </row>
     <row r="31">
@@ -6958,100 +6958,100 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>1571419</v>
+        <v>3762593</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>924236</v>
+        <v>2956425</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4494875</v>
+        <v>9862849</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6835461</v>
+        <v>2638662</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5010623</v>
+        <v>9063386</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8693022</v>
+        <v>2919844</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2344195</v>
+        <v>758359</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>5302598</v>
+        <v>1255078</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2105641</v>
+        <v>6190444</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>921269</v>
+        <v>4115254</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>4346377</v>
+        <v>5058658</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>8333195</v>
+        <v>3517088</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>3718393</v>
+        <v>5953391</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>4848461</v>
+        <v>1579664</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2279199</v>
+        <v>8046724</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>3491739</v>
+        <v>5633030</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>2620912</v>
+        <v>542009</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>8446997</v>
+        <v>8296843</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>6209482</v>
+        <v>623837</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>4102391</v>
+        <v>434552</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>582018</v>
+        <v>5791679</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>6233637</v>
+        <v>8866758</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>5142064</v>
+        <v>1049318</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6853839</v>
+        <v>5113932</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>8595616</v>
+        <v>3950880</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>5117584</v>
+        <v>4402744</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>6743706</v>
+        <v>8662826</v>
       </c>
       <c r="AC31" s="3" t="n">
-        <v>1857602</v>
+        <v>9648108</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>6357996</v>
+        <v>7310685</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>6466293</v>
+        <v>6979449</v>
       </c>
       <c r="AF31" s="3" t="n">
-        <v>2937467</v>
+        <v>7021745</v>
       </c>
       <c r="AG31" s="3" t="n">
-        <v>300669</v>
+        <v>4652917</v>
       </c>
     </row>
     <row r="32">
@@ -7061,100 +7061,100 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>750493</v>
+        <v>6877931</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>6034701</v>
+        <v>1320441</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>2343119</v>
+        <v>9797964</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>9526483</v>
+        <v>1905580</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>8700582</v>
+        <v>8651591</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>293551</v>
+        <v>1810968</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4125993</v>
+        <v>4807077</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8879802</v>
+        <v>8037883</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3971593</v>
+        <v>5366288</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>4490636</v>
+        <v>8350562</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1774894</v>
+        <v>2318780</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>4370336</v>
+        <v>171837</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>9358136</v>
+        <v>9551832</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>5215304</v>
+        <v>945073</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8204497</v>
+        <v>1180469</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>2025023</v>
+        <v>7811728</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>9051420</v>
+        <v>3480759</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>8042134</v>
+        <v>9210849</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>5338317</v>
+        <v>7386857</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>7101205</v>
+        <v>3260381</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>1596308</v>
+        <v>6525476</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>1315186</v>
+        <v>260628</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>227332</v>
+        <v>6406000</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>3081297</v>
+        <v>8746605</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8388527</v>
+        <v>8141123</v>
       </c>
       <c r="AA32" s="3" t="n">
-        <v>9888813</v>
+        <v>6881287</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>2705595</v>
+        <v>3914719</v>
       </c>
       <c r="AC32" s="3" t="n">
-        <v>1920542</v>
+        <v>443702</v>
       </c>
       <c r="AD32" s="3" t="n">
-        <v>494929</v>
+        <v>6623702</v>
       </c>
       <c r="AE32" s="3" t="n">
-        <v>6360803</v>
+        <v>7243600</v>
       </c>
       <c r="AF32" s="3" t="n">
-        <v>8971570</v>
+        <v>3308012</v>
       </c>
       <c r="AG32" s="3" t="n">
-        <v>6847204</v>
+        <v>15658</v>
       </c>
     </row>
     <row r="33">
@@ -7164,100 +7164,100 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>6926371</v>
+        <v>8749976</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>338948</v>
+        <v>4246281</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>9927786</v>
+        <v>460719</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>9616968</v>
+        <v>6184012</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4267933</v>
+        <v>4976676</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5474161</v>
+        <v>2960327</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5418225</v>
+        <v>3301404</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2810451</v>
+        <v>5646264</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2464010</v>
+        <v>5749058</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>3885579</v>
+        <v>5384662</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>5080348</v>
+        <v>1721181</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>4613095</v>
+        <v>8428283</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>7839313</v>
+        <v>4831688</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>5716763</v>
+        <v>4945790</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>8562855</v>
+        <v>5168636</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>5909184</v>
+        <v>8809979</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>50359</v>
+        <v>9205686</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>9233352</v>
+        <v>5532649</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>444056</v>
+        <v>4299049</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>2864522</v>
+        <v>9552244</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>8614370</v>
+        <v>1628803</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>3957876</v>
+        <v>6000595</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>3109981</v>
+        <v>6800061</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>636114</v>
+        <v>2986610</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>9669430</v>
+        <v>8608182</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>83812</v>
+        <v>723512</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>6025287</v>
+        <v>1702555</v>
       </c>
       <c r="AC33" s="3" t="n">
-        <v>1381392</v>
+        <v>8756563</v>
       </c>
       <c r="AD33" s="3" t="n">
-        <v>8345223</v>
+        <v>4047258</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>8247575</v>
+        <v>9260609</v>
       </c>
       <c r="AF33" s="3" t="n">
-        <v>6161833</v>
+        <v>7221867</v>
       </c>
       <c r="AG33" s="3" t="n">
-        <v>320212</v>
+        <v>7001649</v>
       </c>
     </row>
     <row r="34">
@@ -7267,100 +7267,100 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3145400</v>
+        <v>3890476</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2059595</v>
+        <v>1541000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4779804</v>
+        <v>5119566</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>6256110</v>
+        <v>7306361</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1844435</v>
+        <v>5084308</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>7723493</v>
+        <v>6683906</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>6759956</v>
+        <v>4066905</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3114465</v>
+        <v>1892673</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>4254771</v>
+        <v>4794781</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>7142696</v>
+        <v>5821229</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3841794</v>
+        <v>939483</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>7140419</v>
+        <v>6011925</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>7061890</v>
+        <v>7074395</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>726692</v>
+        <v>4414232</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>9362674</v>
+        <v>263791</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3872392</v>
+        <v>8744601</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>8855378</v>
+        <v>3991107</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>2047588</v>
+        <v>2742921</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>172633</v>
+        <v>7173408</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1130526</v>
+        <v>5962169</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2743541</v>
+        <v>1156304</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>9255691</v>
+        <v>6146960</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>1132969</v>
+        <v>2564712</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6954851</v>
+        <v>3801059</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4144486</v>
+        <v>3674996</v>
       </c>
       <c r="AA34" s="3" t="n">
-        <v>122342</v>
+        <v>103801</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>7000629</v>
+        <v>7508560</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>3581156</v>
+        <v>8170744</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>8233220</v>
+        <v>5391949</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>6269220</v>
+        <v>8423412</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>1974628</v>
+        <v>3685226</v>
       </c>
       <c r="AG34" s="3" t="n">
-        <v>3700354</v>
+        <v>4024218</v>
       </c>
     </row>
     <row r="35">
@@ -7370,100 +7370,100 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7239395</v>
+        <v>133385</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>228725</v>
+        <v>6648726</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>5695441</v>
+        <v>3394024</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>8379472</v>
+        <v>3660995</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1047313</v>
+        <v>1048551</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6655681</v>
+        <v>5193307</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1838020</v>
+        <v>6480864</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>9782118</v>
+        <v>4367029</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5000348</v>
+        <v>7898576</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>3798513</v>
+        <v>3169254</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>1776534</v>
+        <v>1389298</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>7438110</v>
+        <v>8232942</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>6916075</v>
+        <v>1441179</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>2031714</v>
+        <v>249441</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2962507</v>
+        <v>8380091</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>2062102</v>
+        <v>578799</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>9268842</v>
+        <v>3358918</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>4884727</v>
+        <v>3990463</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>570581</v>
+        <v>7102895</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>5661727</v>
+        <v>4862654</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>6398727</v>
+        <v>5806448</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>9150731</v>
+        <v>5010512</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>4727146</v>
+        <v>6968831</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>8873694</v>
+        <v>3055126</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>2040661</v>
+        <v>1458434</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>8689972</v>
+        <v>8621085</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>8385717</v>
+        <v>5922710</v>
       </c>
       <c r="AC35" s="3" t="n">
-        <v>3385624</v>
+        <v>705456</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>9887792</v>
+        <v>1604448</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>3812245</v>
+        <v>2688283</v>
       </c>
       <c r="AF35" s="3" t="n">
-        <v>8018075</v>
+        <v>6403086</v>
       </c>
       <c r="AG35" s="3" t="n">
-        <v>2481822</v>
+        <v>9074334</v>
       </c>
     </row>
   </sheetData>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-25 11:29:47</t>
+          <t>2026-04-26 20:37:16</t>
         </is>
       </c>
     </row>
